--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B287FB-430B-4A81-9C1E-BA7ED6FAC18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236D0B6C-B9F9-4F4A-A71D-F81C452F9B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="757" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="1450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="1449">
   <si>
     <t>tab.name</t>
   </si>
@@ -4442,9 +4442,6 @@
   </si>
   <si>
     <t>**√:**</t>
-  </si>
-  <si>
-    <t>Stratum^[Note: In the event of adverse weather or other unforeseen delays, the cruise leader/co-cruise leader is expected to remove transects as needed to ensure completion of the survey. It is important to assess the situation prior to the start of a stratum, and identify the need for removal of transects.]</t>
   </si>
 </sst>
 </file>
@@ -13156,7 +13153,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
-        <v>1449</v>
+        <v>1343</v>
       </c>
       <c r="B1" s="83" t="s">
         <v>1344</v>
@@ -16817,6 +16814,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B79A833CF10F444BBAB252802BF889FD" ma:contentTypeVersion="13" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="13049228d2ebeeda8a7bd52e722cfa58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c01e712b-8f9b-4625-8219-31b20605feb3" xmlns:ns3="2b166a80-dccc-42cc-be33-87bca7e0d87c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e46e14a2803daf40a531882d51ce3d52" ns2:_="" ns3:_="">
     <xsd:import namespace="c01e712b-8f9b-4625-8219-31b20605feb3"/>
@@ -17039,12 +17042,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -17055,6 +17052,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF9CC6E8-490E-4635-9D3F-743AF6F02B4D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17073,16 +17080,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
   <ds:schemaRefs>

--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\github\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03006CFA-A08E-4045-91A2-DEFA192B76DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A83E9EB-DD5C-4DFE-808E-40818AFE6473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" tabRatio="757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1800" windowWidth="29040" windowHeight="17640" tabRatio="757" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="1474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="1474">
   <si>
     <t>tab.name</t>
   </si>
@@ -4226,9 +4226,6 @@
   </si>
   <si>
     <t>Leg4.1_B</t>
-  </si>
-  <si>
-    <t>Bjoern-Erik.Axelsen@hi.no</t>
   </si>
   <si>
     <t>Location</t>
@@ -4520,6 +4517,9 @@
   </si>
   <si>
     <t>Overview of component sampled, and equipment used during the survey. Overview of the gear codes to be used in the Cruise Logger system, detailed information about the rigging of the equipment as well as technical drawings and other specifications of the various equipment can be found in the Nansen wiki site.</t>
+  </si>
+  <si>
+    <t>Bjoern.Erik.Axelsen@hi.no</t>
   </si>
 </sst>
 </file>
@@ -5343,49 +5343,10 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5401,6 +5362,45 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5684,13 +5684,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="235.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="235.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -5722,15 +5722,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -5738,15 +5738,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="109" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
@@ -5754,39 +5754,39 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -5802,28 +5802,28 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -5835,21 +5835,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="5" width="16.453125" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1796875" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="73" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="73" customFormat="1" ht="69" x14ac:dyDescent="0.35">
       <c r="A1" s="74" t="s">
         <v>201</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A2" s="72" t="s">
         <v>212</v>
       </c>
@@ -5907,15 +5907,15 @@
         <v>227</v>
       </c>
       <c r="H2" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I2" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I2" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J2" s="91"/>
       <c r="K2" s="91"/>
     </row>
-    <row r="3" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A3" s="91" t="s">
         <v>217</v>
       </c>
@@ -5923,10 +5923,10 @@
         <v>218</v>
       </c>
       <c r="C3" s="91" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D3" s="91" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E3" s="91"/>
       <c r="F3" s="91" t="s">
@@ -5936,15 +5936,15 @@
         <v>227</v>
       </c>
       <c r="H3" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I3" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I3" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J3" s="91"/>
       <c r="K3" s="91"/>
     </row>
-    <row r="4" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A4" s="91" t="s">
         <v>217</v>
       </c>
@@ -5965,15 +5965,15 @@
         <v>227</v>
       </c>
       <c r="H4" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I4" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I4" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J4" s="91"/>
       <c r="K4" s="91"/>
     </row>
-    <row r="5" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A5" s="91" t="s">
         <v>217</v>
       </c>
@@ -5994,15 +5994,15 @@
         <v>227</v>
       </c>
       <c r="H5" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I5" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I5" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J5" s="91"/>
       <c r="K5" s="91"/>
     </row>
-    <row r="6" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A6" s="91" t="s">
         <v>217</v>
       </c>
@@ -6023,15 +6023,15 @@
         <v>227</v>
       </c>
       <c r="H6" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I6" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I6" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J6" s="91"/>
       <c r="K6" s="91"/>
     </row>
-    <row r="7" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A7" s="91" t="s">
         <v>217</v>
       </c>
@@ -6052,15 +6052,15 @@
         <v>227</v>
       </c>
       <c r="H7" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I7" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I7" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J7" s="91"/>
       <c r="K7" s="91"/>
     </row>
-    <row r="8" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A8" s="91" t="s">
         <v>217</v>
       </c>
@@ -6081,15 +6081,15 @@
         <v>227</v>
       </c>
       <c r="H8" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I8" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I8" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J8" s="91"/>
       <c r="K8" s="91"/>
     </row>
-    <row r="9" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A9" s="91" t="s">
         <v>217</v>
       </c>
@@ -6110,15 +6110,15 @@
         <v>227</v>
       </c>
       <c r="H9" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I9" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I9" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J9" s="91"/>
       <c r="K9" s="91"/>
     </row>
-    <row r="10" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A10" s="91" t="s">
         <v>217</v>
       </c>
@@ -6139,15 +6139,15 @@
         <v>227</v>
       </c>
       <c r="H10" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I10" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I10" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J10" s="91"/>
       <c r="K10" s="91"/>
     </row>
-    <row r="11" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A11" s="91" t="s">
         <v>217</v>
       </c>
@@ -6155,10 +6155,10 @@
         <v>232</v>
       </c>
       <c r="C11" s="91" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D11" s="91" t="s">
         <v>1413</v>
-      </c>
-      <c r="D11" s="91" t="s">
-        <v>1414</v>
       </c>
       <c r="E11" s="91"/>
       <c r="F11" s="91" t="s">
@@ -6168,26 +6168,26 @@
         <v>227</v>
       </c>
       <c r="H11" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I11" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I11" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J11" s="91"/>
       <c r="K11" s="91"/>
     </row>
-    <row r="12" spans="1:11" s="73" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="73" customFormat="1" ht="46" x14ac:dyDescent="0.35">
       <c r="A12" s="91" t="s">
         <v>217</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C12" s="91" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D12" s="91" t="s">
         <v>1415</v>
-      </c>
-      <c r="D12" s="91" t="s">
-        <v>1416</v>
       </c>
       <c r="E12" s="91"/>
       <c r="F12" s="91" t="s">
@@ -6197,20 +6197,20 @@
         <v>227</v>
       </c>
       <c r="H12" s="91" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I12" s="91" t="s">
         <v>1444</v>
-      </c>
-      <c r="I12" s="91" t="s">
-        <v>1445</v>
       </c>
       <c r="J12" s="91"/>
       <c r="K12" s="91"/>
     </row>
-    <row r="13" spans="1:11" s="73" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="73" customFormat="1" ht="57.5" x14ac:dyDescent="0.35">
       <c r="A13" s="91" t="s">
         <v>217</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C13" s="91" t="s">
         <v>221</v>
@@ -6229,12 +6229,12 @@
         <v>228</v>
       </c>
       <c r="I13" s="91" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="J13" s="91"/>
       <c r="K13" s="91"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="15" x14ac:dyDescent="0.35">
       <c r="H14" s="31"/>
     </row>
   </sheetData>
@@ -6245,15 +6245,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.54296875" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>233</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="66" t="s">
         <v>237</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="66" t="s">
         <v>241</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="66" t="s">
         <v>244</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="66" t="s">
         <v>248</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="66" t="s">
         <v>252</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="66" t="s">
         <v>256</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="66" t="s">
         <v>260</v>
       </c>
@@ -6373,27 +6373,27 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="111" t="s">
         <v>1299</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -6403,7 +6403,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>1300</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1311</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>1311</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>1311</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>1311</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>1311</v>
       </c>
@@ -6624,13 +6624,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>233</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>237</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>241</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>244</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>248</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>252</v>
       </c>
@@ -6686,13 +6686,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>233</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>237</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>241</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>244</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>248</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>252</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>256</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>260</v>
       </c>
@@ -6764,15 +6764,15 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="83.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
+    <col min="3" max="3" width="62.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="83.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="79" t="s">
         <v>277</v>
       </c>
@@ -6786,51 +6786,51 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="103" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="122" t="s">
         <v>280</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="122" t="s">
         <v>281</v>
       </c>
-      <c r="C2" s="100" t="s">
-        <v>1394</v>
+      <c r="C2" s="118" t="s">
+        <v>1393</v>
       </c>
       <c r="D2" s="96" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="104"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="101"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="123"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="119"/>
       <c r="D3" s="96" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="120" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="121" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="101" t="s">
-        <v>1395</v>
+      <c r="C4" s="119" t="s">
+        <v>1394</v>
       </c>
       <c r="D4" s="96" t="s">
         <v>1370</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="105"/>
-      <c r="C5" s="101"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="120"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="119"/>
       <c r="D5" s="96" t="s">
         <v>1371</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="80" t="s">
         <v>284</v>
       </c>
@@ -6838,32 +6838,32 @@
         <v>285</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="D6" s="96" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="81" t="s">
         <v>286</v>
       </c>
       <c r="B7" s="84" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D7" s="96" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
-        <v>1435</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="102" t="s">
+        <v>1434</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>190</v>
@@ -6872,12 +6872,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="116" t="s">
-        <v>1437</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="103" t="s">
+        <v>1436</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C9" s="86" t="s">
         <v>191</v>
@@ -6886,29 +6886,29 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A10" s="81" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B10" s="81" t="s">
         <v>1374</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>1436</v>
+      <c r="C10" s="99" t="s">
+        <v>1435</v>
       </c>
       <c r="D10" s="83" t="s">
         <v>1343</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="80"/>
       <c r="B11" s="80"/>
       <c r="C11" s="85"/>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="99" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="80"/>
       <c r="B12" s="80"/>
       <c r="C12" s="85"/>
@@ -6916,21 +6916,21 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="81" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B13" s="81" t="s">
         <v>1375</v>
       </c>
-      <c r="C13" s="117" t="s">
-        <v>1438</v>
+      <c r="C13" s="104" t="s">
+        <v>1437</v>
       </c>
       <c r="D13" s="96" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="80"/>
       <c r="B14" s="80"/>
       <c r="C14" s="85"/>
@@ -6938,7 +6938,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="88"/>
       <c r="B15" s="80"/>
       <c r="C15" s="85"/>
@@ -6946,7 +6946,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="88"/>
       <c r="B16" s="80"/>
       <c r="C16" s="85"/>
@@ -6954,7 +6954,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="88"/>
       <c r="B17" s="80"/>
       <c r="C17" s="85"/>
@@ -6962,7 +6962,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="88"/>
       <c r="B18" s="80"/>
       <c r="C18" s="81" t="s">
@@ -6972,7 +6972,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="88"/>
       <c r="B19" s="80"/>
       <c r="C19" s="80"/>
@@ -6980,7 +6980,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="88"/>
       <c r="B20" s="80"/>
       <c r="C20" s="80"/>
@@ -6988,7 +6988,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="88"/>
       <c r="B21" s="80"/>
       <c r="C21" s="80" t="s">
@@ -6998,7 +6998,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="88"/>
       <c r="B22" s="80"/>
       <c r="C22" s="80" t="s">
@@ -7008,7 +7008,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="88"/>
       <c r="B23" s="80"/>
       <c r="C23" s="80"/>
@@ -7016,7 +7016,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="80"/>
       <c r="B24" s="80"/>
       <c r="C24" s="89" t="s">
@@ -7026,7 +7026,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="81" t="s">
         <v>290</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="80"/>
       <c r="B26" s="80"/>
       <c r="C26" s="85"/>
@@ -7048,7 +7048,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="80"/>
       <c r="B27" s="80"/>
       <c r="C27" s="85"/>
@@ -7056,7 +7056,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="80"/>
       <c r="B28" s="80"/>
       <c r="C28" s="85"/>
@@ -7064,7 +7064,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="80"/>
       <c r="B29" s="80"/>
       <c r="C29" s="85"/>
@@ -7072,7 +7072,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="80"/>
       <c r="B30" s="80"/>
       <c r="C30" s="85"/>
@@ -7080,7 +7080,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="80"/>
       <c r="B31" s="80"/>
       <c r="C31" s="85"/>
@@ -7088,7 +7088,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="80"/>
       <c r="B32" s="80"/>
       <c r="C32" s="85"/>
@@ -7096,7 +7096,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="80"/>
       <c r="B33" s="80"/>
       <c r="C33" s="80" t="s">
@@ -7106,7 +7106,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="80"/>
       <c r="B34" s="80"/>
       <c r="C34" s="80"/>
@@ -7114,7 +7114,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="80"/>
       <c r="B35" s="80"/>
       <c r="C35" s="80"/>
@@ -7122,7 +7122,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="80"/>
       <c r="B36" s="80"/>
       <c r="C36" s="80"/>
@@ -7130,12 +7130,12 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="107" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="100" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B37" s="100" t="s">
         <v>1399</v>
-      </c>
-      <c r="B37" s="107" t="s">
-        <v>1400</v>
       </c>
       <c r="C37" s="98" t="s">
         <v>192</v>
@@ -7144,43 +7144,43 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="108" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="112" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B38" s="114" t="s">
         <v>1401</v>
       </c>
-      <c r="B38" s="109" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C38" s="110" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D38" s="106" t="s">
+      <c r="C38" s="116" t="s">
         <v>1432</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="111"/>
-      <c r="B39" s="112"/>
-      <c r="C39" s="113"/>
+      <c r="D38" s="99" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="113"/>
+      <c r="B39" s="115"/>
+      <c r="C39" s="117"/>
       <c r="D39" s="96" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A40" s="81" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B40" s="90" t="s">
         <v>1376</v>
       </c>
-      <c r="C40" s="114" t="s">
-        <v>1434</v>
+      <c r="C40" s="101" t="s">
+        <v>1433</v>
       </c>
       <c r="D40" s="96" t="s">
         <v>1368</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="81" t="s">
         <v>294</v>
       </c>
@@ -7192,23 +7192,23 @@
       </c>
       <c r="D41" s="81"/>
     </row>
-    <row r="42" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A42" s="81" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B42" s="81"/>
       <c r="C42" s="81"/>
       <c r="D42" s="81"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="87" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B43" s="87" t="s">
         <v>1404</v>
       </c>
-      <c r="B43" s="87" t="s">
-        <v>1405</v>
-      </c>
       <c r="C43" s="87" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D43" s="87"/>
     </row>
@@ -7232,9 +7232,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:H240"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>297</v>
       </c>
@@ -7254,13 +7254,13 @@
         <v>302</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1" s="50" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="51" t="s">
         <v>304</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="51" t="s">
         <v>304</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="51" t="s">
         <v>304</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="51" t="s">
         <v>322</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="51" t="s">
         <v>322</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="51" t="s">
         <v>304</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="51" t="s">
         <v>322</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="51" t="s">
         <v>322</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="51" t="s">
         <v>322</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="51" t="s">
         <v>322</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="51" t="s">
         <v>322</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="51" t="s">
         <v>322</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="51" t="s">
         <v>322</v>
       </c>
@@ -7598,7 +7598,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="51" t="s">
         <v>322</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="51" t="s">
         <v>322</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="51" t="s">
         <v>322</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="51" t="s">
         <v>322</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="51" t="s">
         <v>322</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="51" t="s">
         <v>322</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="51" t="s">
         <v>322</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="51" t="s">
         <v>322</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
         <v>322</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
         <v>322</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="51" t="s">
         <v>322</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="51" t="s">
         <v>415</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="51" t="s">
         <v>415</v>
       </c>
@@ -7936,7 +7936,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="51" t="s">
         <v>415</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="51" t="s">
         <v>415</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="51" t="s">
         <v>415</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="51" t="s">
         <v>415</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="51" t="s">
         <v>415</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="51" t="s">
         <v>415</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="51" t="s">
         <v>415</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="51" t="s">
         <v>415</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="51" t="s">
         <v>415</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="51" t="s">
         <v>415</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="51" t="s">
         <v>415</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="51" t="s">
         <v>415</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="51" t="s">
         <v>415</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="51" t="s">
         <v>415</v>
       </c>
@@ -8300,7 +8300,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="51" t="s">
         <v>486</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="51" t="s">
         <v>486</v>
       </c>
@@ -8352,7 +8352,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="51" t="s">
         <v>486</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="51" t="s">
         <v>486</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="51" t="s">
         <v>486</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="51" t="s">
         <v>486</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="51" t="s">
         <v>486</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="51" t="s">
         <v>486</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="51" t="s">
         <v>486</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="51" t="s">
         <v>486</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="51" t="s">
         <v>486</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="51" t="s">
         <v>486</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="51" t="s">
         <v>486</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="51" t="s">
         <v>543</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="51" t="s">
         <v>486</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="51" t="s">
         <v>486</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="51" t="s">
         <v>486</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="51" t="s">
         <v>543</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="51" t="s">
         <v>543</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="51" t="s">
         <v>486</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="51" t="s">
         <v>543</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="51" t="s">
         <v>543</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="51" t="s">
         <v>543</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="51" t="s">
         <v>543</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="51" t="s">
         <v>543</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="51" t="s">
         <v>543</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="51" t="s">
         <v>543</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="51" t="s">
         <v>543</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="51" t="s">
         <v>543</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="51" t="s">
         <v>543</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="51" t="s">
         <v>543</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="51" t="s">
         <v>622</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="51" t="s">
         <v>543</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="51" t="s">
         <v>622</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="51" t="s">
         <v>622</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="51" t="s">
         <v>622</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="51" t="s">
         <v>622</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="51" t="s">
         <v>622</v>
       </c>
@@ -9288,7 +9288,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="51" t="s">
         <v>622</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="51" t="s">
         <v>622</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="51" t="s">
         <v>622</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="51" t="s">
         <v>622</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="51" t="s">
         <v>622</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="51" t="s">
         <v>622</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="51" t="s">
         <v>622</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="51" t="s">
         <v>622</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="51" t="s">
         <v>622</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="51" t="s">
         <v>622</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="51" t="s">
         <v>622</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="51" t="s">
         <v>622</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="51" t="s">
         <v>700</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="51" t="s">
         <v>700</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="51" t="s">
         <v>700</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="51" t="s">
         <v>700</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="51" t="s">
         <v>700</v>
       </c>
@@ -9730,7 +9730,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="51" t="s">
         <v>700</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="51" t="s">
         <v>700</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="51" t="s">
         <v>700</v>
       </c>
@@ -9808,7 +9808,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="51" t="s">
         <v>700</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="51" t="s">
         <v>700</v>
       </c>
@@ -9860,7 +9860,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="51" t="s">
         <v>700</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="51" t="s">
         <v>700</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="51" t="s">
         <v>700</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="51" t="s">
         <v>700</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="51" t="s">
         <v>700</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="51" t="s">
         <v>700</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="51" t="s">
         <v>700</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="51" t="s">
         <v>700</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="51" t="s">
         <v>700</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="51" t="s">
         <v>700</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="51" t="s">
         <v>700</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="51" t="s">
         <v>700</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="51" t="s">
         <v>700</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="51" t="s">
         <v>700</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="51" t="s">
         <v>700</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="51" t="s">
         <v>700</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="51" t="s">
         <v>700</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="51" t="s">
         <v>700</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="51" t="s">
         <v>700</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="51" t="s">
         <v>700</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="51" t="s">
         <v>700</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="51" t="s">
         <v>700</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="51" t="s">
         <v>700</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="51" t="s">
         <v>700</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="51" t="s">
         <v>700</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="51" t="s">
         <v>700</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="51" t="s">
         <v>700</v>
       </c>
@@ -10562,7 +10562,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="51" t="s">
         <v>700</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="51" t="s">
         <v>700</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="51" t="s">
         <v>700</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="51" t="s">
         <v>859</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="51" t="s">
         <v>700</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="51" t="s">
         <v>700</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="51" t="s">
         <v>700</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="51" t="s">
         <v>859</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="51" t="s">
         <v>859</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="51" t="s">
         <v>700</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="51" t="s">
         <v>700</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="51" t="s">
         <v>700</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="51" t="s">
         <v>859</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="51" t="s">
         <v>859</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="51" t="s">
         <v>700</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="51" t="s">
         <v>700</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="51" t="s">
         <v>700</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="51" t="s">
         <v>700</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="51" t="s">
         <v>859</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="51" t="s">
         <v>859</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="51" t="s">
         <v>700</v>
       </c>
@@ -11108,7 +11108,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="51" t="s">
         <v>700</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="51" t="s">
         <v>859</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="51" t="s">
         <v>859</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="51" t="s">
         <v>700</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="51" t="s">
         <v>700</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="51" t="s">
         <v>700</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="51" t="s">
         <v>700</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="51" t="s">
         <v>859</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="51" t="s">
         <v>859</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="51" t="s">
         <v>700</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="51" t="s">
         <v>700</v>
       </c>
@@ -11394,7 +11394,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="51" t="s">
         <v>700</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="51" t="s">
         <v>700</v>
       </c>
@@ -11446,7 +11446,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="51" t="s">
         <v>700</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="51" t="s">
         <v>700</v>
       </c>
@@ -11498,7 +11498,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="51" t="s">
         <v>700</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="51" t="s">
         <v>700</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="51" t="s">
         <v>700</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="51" t="s">
         <v>700</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="51" t="s">
         <v>700</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="51" t="s">
         <v>700</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="51" t="s">
         <v>700</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="51" t="s">
         <v>859</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="51" t="s">
         <v>859</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="51" t="s">
         <v>700</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="51" t="s">
         <v>700</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="51" t="s">
         <v>859</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="51" t="s">
         <v>859</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="51" t="s">
         <v>700</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="51" t="s">
         <v>700</v>
       </c>
@@ -11888,7 +11888,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="51" t="s">
         <v>700</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="51" t="s">
         <v>700</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="51" t="s">
         <v>700</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="51" t="s">
         <v>700</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="51" t="s">
         <v>859</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="51" t="s">
         <v>859</v>
       </c>
@@ -12044,7 +12044,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="51" t="s">
         <v>700</v>
       </c>
@@ -12070,7 +12070,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="51" t="s">
         <v>700</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="51" t="s">
         <v>700</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="51" t="s">
         <v>700</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="51" t="s">
         <v>859</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="51" t="s">
         <v>700</v>
       </c>
@@ -12200,7 +12200,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="51" t="s">
         <v>700</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="51" t="s">
         <v>700</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="51" t="s">
         <v>700</v>
       </c>
@@ -12278,7 +12278,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="51" t="s">
         <v>700</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="51" t="s">
         <v>700</v>
       </c>
@@ -12330,7 +12330,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="51" t="s">
         <v>700</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="51" t="s">
         <v>700</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="51" t="s">
         <v>700</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="51" t="s">
         <v>700</v>
       </c>
@@ -12434,7 +12434,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="51" t="s">
         <v>700</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="51" t="s">
         <v>700</v>
       </c>
@@ -12486,7 +12486,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="51" t="s">
         <v>700</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="51" t="s">
         <v>700</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="51" t="s">
         <v>700</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="51" t="s">
         <v>700</v>
       </c>
@@ -12590,7 +12590,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="51" t="s">
         <v>700</v>
       </c>
@@ -12616,7 +12616,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="51" t="s">
         <v>700</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="51" t="s">
         <v>700</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="51" t="s">
         <v>700</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="51" t="s">
         <v>700</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="51" t="s">
         <v>700</v>
       </c>
@@ -12746,7 +12746,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="51" t="s">
         <v>700</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="51" t="s">
         <v>700</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="51" t="s">
         <v>700</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="51" t="s">
         <v>700</v>
       </c>
@@ -12850,7 +12850,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="51" t="s">
         <v>700</v>
       </c>
@@ -12876,7 +12876,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="51" t="s">
         <v>700</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="51" t="s">
         <v>700</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="51" t="s">
         <v>700</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="51" t="s">
         <v>700</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="51" t="s">
         <v>622</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="51" t="s">
         <v>622</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="51" t="s">
         <v>700</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="51" t="s">
         <v>700</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="51" t="s">
         <v>700</v>
       </c>
@@ -13110,7 +13110,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="51" t="s">
         <v>700</v>
       </c>
@@ -13136,7 +13136,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="51" t="s">
         <v>700</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="51" t="s">
         <v>622</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="51" t="s">
         <v>622</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="51" t="s">
         <v>622</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="51" t="s">
         <v>700</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="51" t="s">
         <v>700</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="51" t="s">
         <v>622</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="51" t="s">
         <v>622</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="51" t="s">
         <v>622</v>
       </c>
@@ -13370,7 +13370,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="51" t="s">
         <v>700</v>
       </c>
@@ -13396,7 +13396,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="51" t="s">
         <v>700</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="51" t="s">
         <v>622</v>
       </c>
@@ -13448,7 +13448,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="51" t="s">
         <v>622</v>
       </c>
@@ -13482,9 +13482,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="53" t="s">
         <v>1289</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="57" t="s">
         <v>1292</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="61"/>
       <c r="B3" s="55">
         <v>2</v>
@@ -13590,7 +13590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="61"/>
       <c r="B4" s="55">
         <v>3</v>
@@ -13620,7 +13620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="61"/>
       <c r="B5" s="55">
         <v>4</v>
@@ -13650,7 +13650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="61"/>
       <c r="B6" s="55">
         <v>5</v>
@@ -13680,7 +13680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="61"/>
       <c r="B7" s="55">
         <v>6</v>
@@ -13710,7 +13710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="61"/>
       <c r="B8" s="55">
         <v>7</v>
@@ -13742,7 +13742,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="61"/>
       <c r="B9" s="55">
         <v>8</v>
@@ -13772,7 +13772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="61"/>
       <c r="B10" s="55">
         <v>9</v>
@@ -13798,7 +13798,7 @@
       <c r="K10" s="22"/>
       <c r="L10" s="64"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="63"/>
       <c r="B11" s="55">
         <v>10</v>
@@ -13824,7 +13824,7 @@
       <c r="K11" s="22"/>
       <c r="L11" s="64"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="57" t="s">
         <v>1295</v>
       </c>
@@ -13852,7 +13852,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="64"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="61"/>
       <c r="B13" s="55">
         <v>12</v>
@@ -13880,7 +13880,7 @@
       <c r="K13" s="22"/>
       <c r="L13" s="64"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="61"/>
       <c r="B14" s="55">
         <v>13</v>
@@ -13908,7 +13908,7 @@
       <c r="K14" s="22"/>
       <c r="L14" s="64"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="61"/>
       <c r="B15" s="55">
         <v>14</v>
@@ -13934,7 +13934,7 @@
       <c r="K15" s="22"/>
       <c r="L15" s="64"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="61"/>
       <c r="B16" s="55">
         <v>15</v>
@@ -13960,7 +13960,7 @@
       <c r="K16" s="22"/>
       <c r="L16" s="64"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="61"/>
       <c r="B17" s="55">
         <v>16</v>
@@ -13986,7 +13986,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="64"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="61"/>
       <c r="B18" s="55">
         <v>17</v>
@@ -14012,7 +14012,7 @@
       <c r="K18" s="22"/>
       <c r="L18" s="64"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="61"/>
       <c r="B19" s="55">
         <v>18</v>
@@ -14038,7 +14038,7 @@
       <c r="K19" s="22"/>
       <c r="L19" s="64"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="61"/>
       <c r="B20" s="55">
         <v>19</v>
@@ -14064,7 +14064,7 @@
       <c r="K20" s="22"/>
       <c r="L20" s="64"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="63"/>
       <c r="B21" s="55">
         <v>20</v>
@@ -14090,7 +14090,7 @@
       <c r="K21" s="22"/>
       <c r="L21" s="64"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="57" t="s">
         <v>1298</v>
       </c>
@@ -14118,7 +14118,7 @@
       <c r="K22" s="22"/>
       <c r="L22" s="64"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="61"/>
       <c r="B23" s="55">
         <v>22</v>
@@ -14144,7 +14144,7 @@
       <c r="K23" s="22"/>
       <c r="L23" s="64"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="61"/>
       <c r="B24" s="55">
         <v>23</v>
@@ -14166,7 +14166,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="64"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="61"/>
       <c r="B25" s="55">
         <v>24</v>
@@ -14184,7 +14184,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="64"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="61"/>
       <c r="B26" s="55">
         <v>25</v>
@@ -14202,7 +14202,7 @@
       <c r="K26" s="22"/>
       <c r="L26" s="64"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="61"/>
       <c r="B27" s="55">
         <v>26</v>
@@ -14220,7 +14220,7 @@
       <c r="K27" s="22"/>
       <c r="L27" s="64"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="63"/>
       <c r="B28" s="55">
         <v>27</v>
@@ -14246,12 +14246,12 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>1312</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>1314</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>1316</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>1317</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>1318</v>
       </c>
@@ -14291,7 +14291,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>1319</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>1320</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>1321</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>1322</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>1323</v>
       </c>
@@ -14331,7 +14331,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>1324</v>
       </c>
@@ -14339,7 +14339,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>1325</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>1326</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>1327</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>1328</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>1329</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>1331</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>1332</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>1333</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>1334</v>
       </c>
@@ -14420,13 +14420,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="76" t="s">
         <v>30</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1335</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1336</v>
       </c>
@@ -14474,7 +14474,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -14491,16 +14491,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>47</v>
       </c>
@@ -14520,9 +14520,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B2" s="6">
         <v>32</v>
@@ -14540,7 +14540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="33" t="s">
         <v>57</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>59</v>
       </c>
@@ -14590,13 +14590,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="3" width="50.42578125" customWidth="1"/>
+    <col min="2" max="3" width="50.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>33</v>
       </c>
@@ -14607,7 +14607,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>36</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>39</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>42</v>
       </c>
@@ -14640,18 +14640,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>1407</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>1408</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>44</v>
       </c>
@@ -14662,37 +14662,37 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="16"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -14706,22 +14706,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.26953125" customWidth="1"/>
+    <col min="7" max="7" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="25.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="68" t="s">
         <v>60</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="70" t="s">
         <v>72</v>
       </c>
@@ -14787,15 +14787,15 @@
       <c r="I2" s="70"/>
       <c r="J2" s="70"/>
       <c r="K2" s="71" t="str">
-        <f>IF(SUM(G2:J2)=0,"",SUM(G2:J2))</f>
+        <f t="shared" ref="K2:K10" si="1">IF(SUM(G2:J2)=0,"",SUM(G2:J2))</f>
         <v/>
       </c>
       <c r="L2" s="71" t="str">
-        <f>IF(C2=D2,"",IF(K2="", "", C2-(D2+K2)))</f>
+        <f t="shared" ref="L2:L10" si="2">IF(C2=D2,"",IF(K2="", "", C2-(D2+K2)))</f>
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="70" t="s">
         <v>72</v>
       </c>
@@ -14820,15 +14820,15 @@
       </c>
       <c r="J3" s="70"/>
       <c r="K3" s="71">
-        <f>IF(SUM(G3:J3)=0,"",SUM(G3:J3))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L3" s="71" t="str">
-        <f>IF(C3=D3,"",IF(K3="", "", C3-(D3+K3)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="70" t="s">
         <v>72</v>
       </c>
@@ -14847,15 +14847,15 @@
       <c r="I4" s="70"/>
       <c r="J4" s="70"/>
       <c r="K4" s="71" t="str">
-        <f>IF(SUM(G4:J4)=0,"",SUM(G4:J4))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L4" s="71" t="str">
-        <f>IF(C4=D4,"",IF(K4="", "", C4-(D4+K4)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="70" t="s">
         <v>72</v>
       </c>
@@ -14874,15 +14874,15 @@
       <c r="I5" s="70"/>
       <c r="J5" s="70"/>
       <c r="K5" s="71" t="str">
-        <f>IF(SUM(G5:J5)=0,"",SUM(G5:J5))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L5" s="71" t="str">
-        <f>IF(C5=D5,"",IF(K5="", "", C5-(D5+K5)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
         <v>72</v>
       </c>
@@ -14901,15 +14901,15 @@
       <c r="I6" s="70"/>
       <c r="J6" s="70"/>
       <c r="K6" s="71" t="str">
-        <f>IF(SUM(G6:J6)=0,"",SUM(G6:J6))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L6" s="71" t="str">
-        <f>IF(C6=D6,"",IF(K6="", "", C6-(D6+K6)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="70" t="s">
         <v>72</v>
       </c>
@@ -14940,15 +14940,15 @@
       </c>
       <c r="J7" s="70"/>
       <c r="K7" s="71">
-        <f>IF(SUM(G7:J7)=0,"",SUM(G7:J7))</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="L7" s="71">
-        <f>IF(C7=D7,"",IF(K7="", "", C7-(D7+K7)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="70" t="s">
         <v>72</v>
       </c>
@@ -14967,15 +14967,15 @@
       <c r="I8" s="70"/>
       <c r="J8" s="70"/>
       <c r="K8" s="71" t="str">
-        <f>IF(SUM(G8:J8)=0,"",SUM(G8:J8))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L8" s="71" t="str">
-        <f>IF(C8=D8,"",IF(K8="", "", C8-(D8+K8)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="70" t="s">
         <v>72</v>
       </c>
@@ -15000,15 +15000,15 @@
       <c r="I9" s="70"/>
       <c r="J9" s="70"/>
       <c r="K9" s="71" t="str">
-        <f>IF(SUM(G9:J9)=0,"",SUM(G9:J9))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L9" s="71" t="str">
-        <f>IF(C9=D9,"",IF(K9="", "", C9-(D9+K9)))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="70" t="s">
         <v>72</v>
       </c>
@@ -15035,11 +15035,11 @@
       </c>
       <c r="J10" s="70"/>
       <c r="K10" s="71">
-        <f>IF(SUM(G10:J10)=0,"",SUM(G10:J10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L10" s="71">
-        <f>IF(C10=D10,"",IF(K10="", "", C10-(D10+K10)))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M10" s="77">
@@ -15056,18 +15056,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="29" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>82</v>
       </c>
@@ -15090,7 +15090,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15101,7 +15101,7 @@
         <v>73</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>1391</v>
+        <v>1473</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>90</v>
@@ -15113,7 +15113,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15124,7 +15124,7 @@
         <v>94</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>95</v>
@@ -15136,7 +15136,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>94</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>90</v>
@@ -15159,7 +15159,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15216,7 +15216,7 @@
         <v>105</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>90</v>
@@ -15228,7 +15228,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15238,10 +15238,10 @@
       <c r="C8" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="118" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E8" s="119" t="s">
+      <c r="D8" s="105" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E8" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -15251,7 +15251,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15261,10 +15261,10 @@
       <c r="C9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="118" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E9" s="119" t="s">
+      <c r="D9" s="105" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E9" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -15274,7 +15274,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15284,10 +15284,10 @@
       <c r="C10" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="118" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E10" s="119" t="s">
+      <c r="D10" s="105" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E10" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -15297,7 +15297,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15307,10 +15307,10 @@
       <c r="C11" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="118" t="s">
-        <v>1459</v>
-      </c>
-      <c r="E11" s="119" t="s">
+      <c r="D11" s="105" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E11" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -15320,7 +15320,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15330,10 +15330,10 @@
       <c r="C12" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="118" t="s">
-        <v>1460</v>
-      </c>
-      <c r="E12" s="119" t="s">
+      <c r="D12" s="105" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E12" s="106" t="s">
         <v>95</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -15343,7 +15343,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15353,10 +15353,10 @@
       <c r="C13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="118" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E13" s="119" t="s">
+      <c r="D13" s="105" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E13" s="106" t="s">
         <v>95</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -15366,8 +15366,8 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="120" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="107" t="s">
         <v>1388</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -15376,10 +15376,10 @@
       <c r="C14" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="118" t="s">
-        <v>1464</v>
-      </c>
-      <c r="E14" s="119" t="s">
+      <c r="D14" s="105" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E14" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F14" s="5" t="s">
@@ -15389,7 +15389,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>1388</v>
       </c>
@@ -15399,10 +15399,10 @@
       <c r="C15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="118" t="s">
-        <v>1466</v>
-      </c>
-      <c r="E15" s="119" t="s">
+      <c r="D15" s="105" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E15" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F15" s="5" t="s">
@@ -15412,99 +15412,99 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>1388</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>1451</v>
-      </c>
-      <c r="E16" s="119" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E16" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>1388</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E17" s="119" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E17" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="121" t="s">
-        <v>1470</v>
+      <c r="F17" s="108" t="s">
+        <v>1469</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>1388</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>1453</v>
-      </c>
-      <c r="E18" s="119" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E18" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="121" t="s">
-        <v>1470</v>
+      <c r="F18" s="108" t="s">
+        <v>1469</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>1388</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E19" s="119" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E19" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="121" t="s">
-        <v>1470</v>
+      <c r="F19" s="108" t="s">
+        <v>1469</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>1389</v>
       </c>
@@ -15515,9 +15515,9 @@
         <v>115</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>1442</v>
-      </c>
-      <c r="E20" s="119" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E20" s="106" t="s">
         <v>95</v>
       </c>
       <c r="F20" s="5" t="s">
@@ -15527,7 +15527,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1389</v>
       </c>
@@ -15537,10 +15537,10 @@
       <c r="C21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="118" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E21" s="119" t="s">
+      <c r="D21" s="105" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E21" s="106" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="5" t="s">
@@ -15550,7 +15550,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>1389</v>
       </c>
@@ -15560,10 +15560,10 @@
       <c r="C22" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="118" t="s">
-        <v>1463</v>
-      </c>
-      <c r="E22" s="119" t="s">
+      <c r="D22" s="105" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E22" s="106" t="s">
         <v>90</v>
       </c>
       <c r="F22" s="5" t="s">
@@ -15573,7 +15573,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>1389</v>
       </c>
@@ -15583,10 +15583,10 @@
       <c r="C23" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="118" t="s">
-        <v>1467</v>
-      </c>
-      <c r="E23" s="119" t="s">
+      <c r="D23" s="105" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E23" s="106" t="s">
         <v>95</v>
       </c>
       <c r="F23" s="5" t="s">
@@ -15596,7 +15596,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>1390</v>
       </c>
@@ -15609,17 +15609,17 @@
       <c r="D24" s="25" t="s">
         <v>1385</v>
       </c>
-      <c r="E24" s="119" t="s">
+      <c r="E24" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="121" t="s">
+      <c r="F24" s="108" t="s">
         <v>106</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>1390</v>
       </c>
@@ -15630,19 +15630,19 @@
         <v>105</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E25" s="119" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E25" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="121" t="s">
+      <c r="F25" s="108" t="s">
         <v>106</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>1390</v>
       </c>
@@ -15652,20 +15652,20 @@
       <c r="C26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="118" t="s">
-        <v>1465</v>
-      </c>
-      <c r="E26" s="119" t="s">
+      <c r="D26" s="105" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E26" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="121" t="s">
+      <c r="F26" s="108" t="s">
         <v>106</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>1390</v>
       </c>
@@ -15675,20 +15675,20 @@
       <c r="C27" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="118" t="s">
-        <v>1463</v>
-      </c>
-      <c r="E27" s="119" t="s">
+      <c r="D27" s="105" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E27" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="121" t="s">
+      <c r="F27" s="108" t="s">
         <v>106</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>1386</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -15696,7 +15696,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -15704,7 +15704,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -15712,7 +15712,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -15720,10 +15720,10 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="26"/>
@@ -15732,7 +15732,7 @@
       <c r="F33" s="14"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="26"/>
@@ -15741,7 +15741,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="15"/>
       <c r="B35" s="23"/>
       <c r="C35" s="26"/>
@@ -15750,7 +15750,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="15"/>
       <c r="B36" s="23"/>
       <c r="C36" s="26"/>
@@ -15759,7 +15759,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="15"/>
       <c r="B37" s="15"/>
       <c r="C37" s="26"/>
@@ -15768,7 +15768,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="26"/>
@@ -15777,7 +15777,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="15"/>
       <c r="B39" s="15"/>
       <c r="C39" s="26"/>
@@ -15786,7 +15786,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
       <c r="C40" s="26"/>
@@ -15795,7 +15795,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="26"/>
@@ -15804,7 +15804,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="15"/>
       <c r="B42" s="23"/>
       <c r="C42" s="26"/>
@@ -15813,7 +15813,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="15"/>
       <c r="B43" s="23"/>
       <c r="C43" s="26"/>
@@ -15822,7 +15822,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="26"/>
@@ -15831,7 +15831,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="15"/>
       <c r="B45" s="23"/>
       <c r="C45" s="26"/>
@@ -15840,7 +15840,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="26"/>
@@ -15849,7 +15849,7 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
       <c r="C47" s="26"/>
@@ -15858,7 +15858,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="15"/>
       <c r="B48" s="23"/>
       <c r="C48" s="27"/>
@@ -15867,7 +15867,7 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="15"/>
       <c r="B49" s="5"/>
       <c r="C49" s="27"/>
@@ -15876,7 +15876,7 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="30"/>
       <c r="C50" s="27"/>
@@ -15885,7 +15885,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="23"/>
       <c r="C51" s="27"/>
@@ -15927,13 +15927,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="124" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
@@ -15941,7 +15941,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -15949,61 +15949,61 @@
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>129</v>
       </c>
       <c r="B3" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -16019,19 +16019,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
@@ -16057,11 +16057,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="108" t="s">
         <v>149</v>
       </c>
       <c r="C2" s="97" t="s">
@@ -16073,11 +16073,11 @@
       <c r="G2" s="97"/>
       <c r="H2" s="97"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="121" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="108" t="s">
         <v>151</v>
       </c>
       <c r="C3" s="97"/>
@@ -16089,11 +16089,11 @@
       <c r="G3" s="97"/>
       <c r="H3" s="97"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="121" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="108" t="s">
         <v>152</v>
       </c>
       <c r="C4" s="97"/>
@@ -16105,11 +16105,11 @@
       <c r="G4" s="97"/>
       <c r="H4" s="97"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="121" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="121" t="s">
+      <c r="B5" s="108" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="97"/>
@@ -16121,11 +16121,11 @@
       <c r="G5" s="97"/>
       <c r="H5" s="97"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="121" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="108" t="s">
         <v>154</v>
       </c>
       <c r="C6" s="97" t="s">
@@ -16133,15 +16133,15 @@
       </c>
       <c r="D6" s="97"/>
       <c r="E6" s="97"/>
-      <c r="F6" s="121"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="97"/>
       <c r="H6" s="97"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="121" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="108" t="s">
         <v>155</v>
       </c>
       <c r="C7" s="97"/>
@@ -16153,11 +16153,11 @@
       <c r="G7" s="97"/>
       <c r="H7" s="97"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="121" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="108" t="s">
         <v>156</v>
       </c>
       <c r="C8" s="97"/>
@@ -16169,43 +16169,43 @@
       <c r="G8" s="97"/>
       <c r="H8" s="97"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="121" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="121" t="s">
+      <c r="B9" s="108" t="s">
         <v>157</v>
       </c>
       <c r="C9" s="97"/>
       <c r="D9" s="97"/>
       <c r="E9" s="97"/>
-      <c r="F9" s="123" t="s">
+      <c r="F9" s="110" t="s">
         <v>150</v>
       </c>
       <c r="G9" s="97"/>
       <c r="H9" s="97"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="121" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="108" t="s">
         <v>158</v>
       </c>
       <c r="C10" s="97"/>
       <c r="D10" s="97"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="123" t="s">
+      <c r="E10" s="108"/>
+      <c r="F10" s="110" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="97"/>
       <c r="H10" s="97"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="121" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="108" t="s">
         <v>160</v>
       </c>
       <c r="C11" s="97"/>
@@ -16217,11 +16217,11 @@
       <c r="G11" s="97"/>
       <c r="H11" s="97"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="121" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="121" t="s">
+      <c r="B12" s="108" t="s">
         <v>161</v>
       </c>
       <c r="C12" s="97"/>
@@ -16233,11 +16233,11 @@
       <c r="G12" s="97"/>
       <c r="H12" s="97"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="121" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="108" t="s">
         <v>162</v>
       </c>
       <c r="C13" s="97"/>
@@ -16249,11 +16249,11 @@
       <c r="G13" s="97"/>
       <c r="H13" s="97"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="121" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="108" t="s">
         <v>163</v>
       </c>
       <c r="C14" s="97"/>
@@ -16265,11 +16265,11 @@
       <c r="G14" s="97"/>
       <c r="H14" s="97"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="121" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="121" t="s">
+      <c r="B15" s="108" t="s">
         <v>164</v>
       </c>
       <c r="C15" s="97"/>
@@ -16281,11 +16281,11 @@
       <c r="G15" s="97"/>
       <c r="H15" s="97"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="121" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="108" t="s">
         <v>165</v>
       </c>
       <c r="C16" s="97"/>
@@ -16297,11 +16297,11 @@
       <c r="G16" s="97"/>
       <c r="H16" s="97"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="121" t="s">
+      <c r="B17" s="108" t="s">
         <v>166</v>
       </c>
       <c r="C17" s="97"/>
@@ -16313,14 +16313,14 @@
       <c r="G17" s="97"/>
       <c r="H17" s="97"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="121" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="121" t="s">
+      <c r="B18" s="108" t="s">
         <v>167</v>
       </c>
-      <c r="C18" s="121"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="97"/>
       <c r="E18" s="97"/>
       <c r="F18" s="97" t="s">
@@ -16329,14 +16329,14 @@
       <c r="G18" s="97"/>
       <c r="H18" s="97"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="121" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="121" t="s">
+      <c r="B19" s="108" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="121"/>
+      <c r="C19" s="108"/>
       <c r="D19" s="97"/>
       <c r="E19" s="97"/>
       <c r="F19" s="97" t="s">
@@ -16345,14 +16345,14 @@
       <c r="G19" s="97"/>
       <c r="H19" s="97"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="121" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="121" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C20" s="121"/>
+      <c r="B20" s="108" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C20" s="108"/>
       <c r="D20" s="97"/>
       <c r="E20" s="97"/>
       <c r="F20" s="97" t="s">
@@ -16361,14 +16361,14 @@
       <c r="G20" s="97"/>
       <c r="H20" s="97"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="121" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="121" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C21" s="121"/>
+      <c r="B21" s="108" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C21" s="108"/>
       <c r="D21" s="97"/>
       <c r="E21" s="97"/>
       <c r="F21" s="97" t="s">
@@ -16377,11 +16377,11 @@
       <c r="G21" s="97"/>
       <c r="H21" s="97"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="121" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="108" t="s">
         <v>170</v>
       </c>
       <c r="C22" s="97" t="s">
@@ -16393,11 +16393,11 @@
       <c r="G22" s="97"/>
       <c r="H22" s="97"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="121" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="108" t="s">
         <v>171</v>
       </c>
       <c r="C23" s="97"/>
@@ -16409,15 +16409,15 @@
       <c r="G23" s="97"/>
       <c r="H23" s="97"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="121" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="B24" s="121" t="s">
+      <c r="B24" s="108" t="s">
         <v>131</v>
       </c>
       <c r="C24" s="97"/>
-      <c r="D24" s="121"/>
+      <c r="D24" s="108"/>
       <c r="E24" s="97"/>
       <c r="F24" s="97" t="s">
         <v>150</v>
@@ -16425,11 +16425,11 @@
       <c r="G24" s="97"/>
       <c r="H24" s="97"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="121" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="108" t="s">
         <v>172</v>
       </c>
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="108" t="s">
         <v>173</v>
       </c>
       <c r="C25" s="97"/>
@@ -16441,11 +16441,11 @@
       <c r="G25" s="97"/>
       <c r="H25" s="97"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="121" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="121" t="s">
+      <c r="B26" s="108" t="s">
         <v>175</v>
       </c>
       <c r="C26" s="97"/>
@@ -16457,11 +16457,11 @@
       <c r="G26" s="97"/>
       <c r="H26" s="97"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="121" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="B27" s="121" t="s">
+      <c r="B27" s="108" t="s">
         <v>176</v>
       </c>
       <c r="C27" s="97"/>
@@ -16473,26 +16473,26 @@
       <c r="G27" s="97"/>
       <c r="H27" s="97"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="121" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="121" t="s">
-        <v>1471</v>
+      <c r="B28" s="108" t="s">
+        <v>1470</v>
       </c>
       <c r="D28" s="97"/>
       <c r="E28" s="95" t="s">
         <v>150</v>
       </c>
-      <c r="F28" s="121"/>
+      <c r="F28" s="108"/>
       <c r="G28" s="97"/>
       <c r="H28" s="97"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="121" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="121" t="s">
+      <c r="B29" s="108" t="s">
         <v>177</v>
       </c>
       <c r="C29" s="97" t="s">
@@ -16504,21 +16504,21 @@
       <c r="G29" s="97"/>
       <c r="H29" s="97"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="121" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121" t="s">
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108" t="s">
         <v>150</v>
       </c>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16529,14 +16529,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="37" t="s">
         <v>179</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="40" t="s">
         <v>190</v>
       </c>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="M2" s="43"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>191</v>
       </c>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="M3" s="43"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="40" t="s">
         <v>192</v>
       </c>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>193</v>
       </c>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="M5" s="43"/>
     </row>
-    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="40" t="s">
         <v>194</v>
       </c>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="M6" s="43"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="40" t="s">
         <v>195</v>
       </c>
@@ -16733,7 +16733,7 @@
       <c r="J7" s="18"/>
       <c r="M7" s="43"/>
     </row>
-    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40" t="s">
         <v>196</v>
       </c>
@@ -16755,7 +16755,7 @@
       </c>
       <c r="M8" s="43"/>
     </row>
-    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="40" t="s">
         <v>197</v>
       </c>
@@ -16774,7 +16774,7 @@
       <c r="J9" s="18"/>
       <c r="M9" s="43"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="45" t="s">
         <v>198</v>
       </c>
@@ -16796,14 +16796,16 @@
       </c>
       <c r="M10" s="43"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="45" t="s">
         <v>199</v>
       </c>
       <c r="B11" s="41" t="s">
         <v>1378</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="41" t="s">
+        <v>1378</v>
+      </c>
       <c r="D11" s="19"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
@@ -16815,7 +16817,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="46" t="s">
         <v>200</v>
       </c>
@@ -16834,7 +16836,7 @@
       <c r="L12" s="48"/>
       <c r="M12" s="49"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="41" t="s">
         <v>1383</v>
       </c>
@@ -16853,7 +16855,7 @@
       <c r="L13" s="78"/>
       <c r="M13" s="78"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="42" t="s">
         <v>1384</v>
       </c>
@@ -16872,7 +16874,7 @@
       <c r="L14" s="78"/>
       <c r="M14" s="78"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="20"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -16882,7 +16884,7 @@
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="20"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -16892,7 +16894,7 @@
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="20"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -16902,7 +16904,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="20"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -16912,7 +16914,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="20"/>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -16922,7 +16924,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="20"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -16932,7 +16934,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="20"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -16942,7 +16944,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="20"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -16952,12 +16954,12 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="20"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="16"/>
       <c r="B24" s="19"/>
     </row>

--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70129490-143E-4C41-AA83-B229642FE56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10C3545-40F5-469A-964D-34A42A19DF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="757" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21390" tabRatio="757" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -4147,9 +4147,6 @@
     <t>*Trachurus trecae*</t>
   </si>
   <si>
-    <t>*Trachurus picturatus*</t>
-  </si>
-  <si>
     <t>*Scomber colias*</t>
   </si>
   <si>
@@ -4511,6 +4508,9 @@
   </si>
   <si>
     <t>sardine and round herring eggs</t>
+  </si>
+  <si>
+    <t>*Trachurus capensis*</t>
   </si>
 </sst>
 </file>
@@ -5721,7 +5721,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5753,7 +5753,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5769,7 +5769,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5777,7 +5777,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5801,7 +5801,7 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5809,7 +5809,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5817,7 +5817,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
   </sheetData>
@@ -5883,7 +5883,7 @@
         <v>207</v>
       </c>
       <c r="B2" s="91" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C2" s="91" t="s">
         <v>208</v>
@@ -5901,10 +5901,10 @@
         <v>221</v>
       </c>
       <c r="H2" s="91" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="I2" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J2" s="91"/>
       <c r="K2" s="91"/>
@@ -5917,10 +5917,10 @@
         <v>212</v>
       </c>
       <c r="C3" s="91" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="D3" s="91" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E3" s="91"/>
       <c r="F3" s="91" t="s">
@@ -5933,7 +5933,7 @@
         <v>103</v>
       </c>
       <c r="I3" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J3" s="91"/>
       <c r="K3" s="91"/>
@@ -5962,7 +5962,7 @@
         <v>103</v>
       </c>
       <c r="I4" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J4" s="91"/>
       <c r="K4" s="91"/>
@@ -5991,7 +5991,7 @@
         <v>103</v>
       </c>
       <c r="I5" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J5" s="91"/>
       <c r="K5" s="91"/>
@@ -6020,7 +6020,7 @@
         <v>103</v>
       </c>
       <c r="I6" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J6" s="91"/>
       <c r="K6" s="91"/>
@@ -6049,7 +6049,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J7" s="91"/>
       <c r="K7" s="91"/>
@@ -6078,7 +6078,7 @@
         <v>103</v>
       </c>
       <c r="I8" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J8" s="91"/>
       <c r="K8" s="91"/>
@@ -6107,7 +6107,7 @@
         <v>103</v>
       </c>
       <c r="I9" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J9" s="91"/>
       <c r="K9" s="91"/>
@@ -6136,7 +6136,7 @@
         <v>103</v>
       </c>
       <c r="I10" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J10" s="91"/>
       <c r="K10" s="91"/>
@@ -6149,10 +6149,10 @@
         <v>225</v>
       </c>
       <c r="C11" s="91" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D11" s="91" t="s">
         <v>1404</v>
-      </c>
-      <c r="D11" s="91" t="s">
-        <v>1405</v>
       </c>
       <c r="E11" s="91"/>
       <c r="F11" s="91" t="s">
@@ -6165,7 +6165,7 @@
         <v>103</v>
       </c>
       <c r="I11" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J11" s="91"/>
       <c r="K11" s="91"/>
@@ -6175,13 +6175,13 @@
         <v>211</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C12" s="91" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D12" s="91" t="s">
         <v>1406</v>
-      </c>
-      <c r="D12" s="91" t="s">
-        <v>1407</v>
       </c>
       <c r="E12" s="91"/>
       <c r="F12" s="91" t="s">
@@ -6194,7 +6194,7 @@
         <v>103</v>
       </c>
       <c r="I12" s="91" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J12" s="91"/>
       <c r="K12" s="91"/>
@@ -6204,7 +6204,7 @@
         <v>211</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C13" s="91" t="s">
         <v>215</v>
@@ -6220,10 +6220,10 @@
         <v>221</v>
       </c>
       <c r="H13" s="91" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="I13" s="91" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="J13" s="91"/>
       <c r="K13" s="91"/>
@@ -6788,7 +6788,7 @@
         <v>274</v>
       </c>
       <c r="C2" s="119" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="D2" s="96" t="s">
         <v>1335</v>
@@ -6810,7 +6810,7 @@
         <v>276</v>
       </c>
       <c r="C4" s="120" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D4" s="96" t="s">
         <v>1363</v>
@@ -6821,7 +6821,7 @@
       <c r="B5" s="122"/>
       <c r="C5" s="120"/>
       <c r="D5" s="96" t="s">
-        <v>1364</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6832,10 +6832,10 @@
         <v>278</v>
       </c>
       <c r="C6" s="82" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D6" s="96" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6843,10 +6843,10 @@
         <v>279</v>
       </c>
       <c r="B7" s="84" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D7" s="96" t="s">
         <v>189</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="102" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C8" s="92" t="s">
         <v>185</v>
@@ -6868,10 +6868,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="103" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C9" s="86" t="s">
         <v>186</v>
@@ -6882,13 +6882,13 @@
     </row>
     <row r="10" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A10" s="81" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C10" s="99" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D10" s="83" t="s">
         <v>1336</v>
@@ -6912,13 +6912,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="81" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B13" s="81" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C13" s="104" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D13" s="96" t="s">
         <v>1337</v>
@@ -7017,7 +7017,7 @@
         <v>1348</v>
       </c>
       <c r="D24" s="96" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -7126,10 +7126,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="100" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B37" s="100" t="s">
         <v>1391</v>
-      </c>
-      <c r="B37" s="100" t="s">
-        <v>1392</v>
       </c>
       <c r="C37" s="98" t="s">
         <v>187</v>
@@ -7140,16 +7140,16 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="113" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B38" s="115" t="s">
         <v>1393</v>
       </c>
-      <c r="B38" s="115" t="s">
-        <v>1394</v>
-      </c>
       <c r="C38" s="117" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="D38" s="99" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -7162,13 +7162,13 @@
     </row>
     <row r="40" spans="1:4" ht="39" x14ac:dyDescent="0.25">
       <c r="A40" s="81" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B40" s="90" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C40" s="101" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="D40" s="96" t="s">
         <v>1361</v>
@@ -7188,7 +7188,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="81" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B42" s="81" t="s">
         <v>194</v>
@@ -7202,13 +7202,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="87" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B43" s="87" t="s">
         <v>1395</v>
       </c>
-      <c r="B43" s="87" t="s">
-        <v>1396</v>
-      </c>
       <c r="C43" s="87" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="D43" s="87"/>
     </row>
@@ -7254,7 +7254,7 @@
         <v>295</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1" s="50" t="s">
         <v>296</v>
@@ -14522,7 +14522,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B2" s="6">
         <v>32</v>
@@ -14642,13 +14642,13 @@
     </row>
     <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>1398</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>1399</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -14748,7 +14748,7 @@
         <v>68</v>
       </c>
       <c r="M1" s="68" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -15081,7 +15081,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>86</v>
@@ -15090,7 +15090,7 @@
         <v>70</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>87</v>
@@ -15104,7 +15104,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>90</v>
@@ -15113,7 +15113,7 @@
         <v>91</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>92</v>
@@ -15127,7 +15127,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>94</v>
@@ -15136,7 +15136,7 @@
         <v>91</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>87</v>
@@ -15150,7 +15150,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>95</v>
@@ -15173,7 +15173,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>98</v>
@@ -15196,7 +15196,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>101</v>
@@ -15205,7 +15205,7 @@
         <v>102</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>87</v>
@@ -15214,12 +15214,12 @@
         <v>103</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>104</v>
@@ -15228,7 +15228,7 @@
         <v>102</v>
       </c>
       <c r="D8" s="105" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E8" s="106" t="s">
         <v>87</v>
@@ -15237,12 +15237,12 @@
         <v>103</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>105</v>
@@ -15251,7 +15251,7 @@
         <v>102</v>
       </c>
       <c r="D9" s="105" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E9" s="106" t="s">
         <v>87</v>
@@ -15260,12 +15260,12 @@
         <v>103</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>106</v>
@@ -15274,7 +15274,7 @@
         <v>102</v>
       </c>
       <c r="D10" s="105" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E10" s="106" t="s">
         <v>87</v>
@@ -15283,12 +15283,12 @@
         <v>103</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>107</v>
@@ -15297,7 +15297,7 @@
         <v>102</v>
       </c>
       <c r="D11" s="105" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="E11" s="106" t="s">
         <v>87</v>
@@ -15306,12 +15306,12 @@
         <v>103</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>108</v>
@@ -15320,7 +15320,7 @@
         <v>102</v>
       </c>
       <c r="D12" s="105" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>92</v>
@@ -15329,12 +15329,12 @@
         <v>103</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>109</v>
@@ -15343,7 +15343,7 @@
         <v>102</v>
       </c>
       <c r="D13" s="105" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="E13" s="106" t="s">
         <v>92</v>
@@ -15352,12 +15352,12 @@
         <v>110</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>115</v>
@@ -15366,7 +15366,7 @@
         <v>116</v>
       </c>
       <c r="D14" s="105" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E14" s="106" t="s">
         <v>87</v>
@@ -15375,12 +15375,12 @@
         <v>103</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>118</v>
@@ -15389,7 +15389,7 @@
         <v>116</v>
       </c>
       <c r="D15" s="105" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="E15" s="106" t="s">
         <v>87</v>
@@ -15398,104 +15398,104 @@
         <v>110</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E16" s="106" t="s">
         <v>87</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E17" s="106" t="s">
         <v>92</v>
       </c>
       <c r="F17" s="108" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E18" s="106" t="s">
         <v>87</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E19" s="106" t="s">
         <v>92</v>
       </c>
       <c r="F19" s="108" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>111</v>
@@ -15504,7 +15504,7 @@
         <v>112</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E20" s="106" t="s">
         <v>92</v>
@@ -15513,12 +15513,12 @@
         <v>103</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>113</v>
@@ -15527,7 +15527,7 @@
         <v>102</v>
       </c>
       <c r="D21" s="105" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="E21" s="106" t="s">
         <v>92</v>
@@ -15536,12 +15536,12 @@
         <v>103</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>114</v>
@@ -15550,7 +15550,7 @@
         <v>102</v>
       </c>
       <c r="D22" s="105" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="E22" s="106" t="s">
         <v>87</v>
@@ -15559,12 +15559,12 @@
         <v>103</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>117</v>
@@ -15573,7 +15573,7 @@
         <v>116</v>
       </c>
       <c r="D23" s="105" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E23" s="106" t="s">
         <v>92</v>
@@ -15582,12 +15582,12 @@
         <v>103</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>119</v>
@@ -15596,7 +15596,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="E24" s="106" t="s">
         <v>87</v>
@@ -15605,12 +15605,12 @@
         <v>103</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>120</v>
@@ -15619,7 +15619,7 @@
         <v>102</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E25" s="106" t="s">
         <v>87</v>
@@ -15628,12 +15628,12 @@
         <v>103</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>121</v>
@@ -15642,7 +15642,7 @@
         <v>102</v>
       </c>
       <c r="D26" s="105" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E26" s="106" t="s">
         <v>87</v>
@@ -15651,12 +15651,12 @@
         <v>103</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>114</v>
@@ -15665,7 +15665,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="105" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="E27" s="106" t="s">
         <v>87</v>
@@ -15674,7 +15674,7 @@
         <v>103</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -15943,7 +15943,7 @@
         <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -15966,7 +15966,7 @@
         <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -15974,7 +15974,7 @@
         <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -15997,7 +15997,7 @@
         <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
   </sheetData>
@@ -16339,7 +16339,7 @@
         <v>155</v>
       </c>
       <c r="B20" s="108" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C20" s="108"/>
       <c r="D20" s="97"/>
@@ -16355,7 +16355,7 @@
         <v>155</v>
       </c>
       <c r="B21" s="108" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C21" s="108"/>
       <c r="D21" s="97"/>
@@ -16467,7 +16467,7 @@
         <v>170</v>
       </c>
       <c r="B28" s="108" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D28" s="97"/>
       <c r="E28" s="95" t="s">
@@ -16482,7 +16482,7 @@
         <v>170</v>
       </c>
       <c r="B29" s="108" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C29" s="97" t="s">
         <v>146</v>
@@ -16557,7 +16557,7 @@
         <v>169</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="L1" s="38" t="s">
         <v>183</v>
@@ -16571,27 +16571,27 @@
         <v>185</v>
       </c>
       <c r="B2" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G2" s="42" t="s">
         <v>1371</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E2" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>1372</v>
       </c>
       <c r="H2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M2" s="43"/>
     </row>
@@ -16600,29 +16600,29 @@
         <v>186</v>
       </c>
       <c r="B3" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>1371</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>1372</v>
       </c>
       <c r="H3" s="18"/>
       <c r="J3" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M3" s="43"/>
     </row>
@@ -16631,10 +16631,10 @@
         <v>187</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="18"/>
@@ -16644,7 +16644,7 @@
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M4" s="43"/>
     </row>
@@ -16653,10 +16653,10 @@
         <v>188</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="18"/>
@@ -16666,7 +16666,7 @@
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M5" s="43"/>
     </row>
@@ -16675,29 +16675,29 @@
         <v>189</v>
       </c>
       <c r="B6" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>1371</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="H6" s="42" t="s">
         <v>1371</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>1372</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>1372</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M6" s="43"/>
     </row>
@@ -16706,10 +16706,10 @@
         <v>190</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="18"/>
@@ -16717,7 +16717,7 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
       <c r="I7" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="J7" s="18"/>
       <c r="M7" s="43"/>
@@ -16727,10 +16727,10 @@
         <v>191</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="18"/>
@@ -16740,7 +16740,7 @@
       <c r="I8" s="44"/>
       <c r="J8" s="18"/>
       <c r="L8" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M8" s="43"/>
     </row>
@@ -16749,10 +16749,10 @@
         <v>192</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="18"/>
@@ -16768,10 +16768,10 @@
         <v>193</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="18"/>
@@ -16781,7 +16781,7 @@
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
       <c r="L10" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M10" s="43"/>
     </row>
@@ -16790,10 +16790,10 @@
         <v>194</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="18"/>
@@ -16803,7 +16803,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="M11" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -16811,7 +16811,7 @@
         <v>195</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="47"/>
@@ -16827,10 +16827,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B13" s="78" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C13" s="78"/>
       <c r="D13" s="78"/>
@@ -16846,10 +16846,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="78"/>
@@ -16959,6 +16959,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B79A833CF10F444BBAB252802BF889FD" ma:contentTypeVersion="13" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="13049228d2ebeeda8a7bd52e722cfa58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c01e712b-8f9b-4625-8219-31b20605feb3" xmlns:ns3="2b166a80-dccc-42cc-be33-87bca7e0d87c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e46e14a2803daf40a531882d51ce3d52" ns2:_="" ns3:_="">
     <xsd:import namespace="c01e712b-8f9b-4625-8219-31b20605feb3"/>
@@ -17181,22 +17196,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF9CC6E8-490E-4635-9D3F-743AF6F02B4D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17213,22 +17231,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a5213\ownCloud\Nansen\Leg 5.1 2022\SailingOrder\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB80BED-E2F8-4E1C-813C-708920FCA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0B111A-F04C-4B36-BC58-042DF85D3F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18210" yWindow="4365" windowWidth="23025" windowHeight="9360" tabRatio="757" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24465" yWindow="9480" windowWidth="23025" windowHeight="9360" tabRatio="757" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="592">
   <si>
     <t>tab.name</t>
   </si>
@@ -928,22 +928,7 @@
     <t>Octopodidae - Benthic octopods</t>
   </si>
   <si>
-    <t>anchovyfat</t>
-  </si>
-  <si>
-    <t>sardinefat</t>
-  </si>
-  <si>
-    <t>Fat stage scale for anchovy to be used during Leg 4.1</t>
-  </si>
-  <si>
-    <t>Fat stage scale for sardine and round sardinella to be used during Leg 4.1</t>
-  </si>
-  <si>
     <t>Labelled Eppendorf vials to be used for storing genetic samples</t>
-  </si>
-  <si>
-    <t>Leg 4.1 survey acoustic transects and strata in South-West Africa for small pelagic recruitment purposes.</t>
   </si>
   <si>
     <t>Community structure of mesopelagic fish</t>
@@ -1886,6 +1871,9 @@
   </si>
   <si>
     <t>North</t>
+  </si>
+  <si>
+    <t>Leg 5 survey acoustic transects in Northwest Africa to assess the abundance and distribution of transboundary pelagic resources.</t>
   </si>
 </sst>
 </file>
@@ -3081,7 +3069,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3113,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3121,7 +3109,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3129,7 +3117,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3137,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3161,7 +3149,7 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3169,7 +3157,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3177,7 +3165,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -3243,7 +3231,7 @@
         <v>157</v>
       </c>
       <c r="B2" s="89" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C2" s="89" t="s">
         <v>158</v>
@@ -3261,10 +3249,10 @@
         <v>171</v>
       </c>
       <c r="H2" s="89" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I2" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J2" s="89"/>
       <c r="K2" s="89"/>
@@ -3277,10 +3265,10 @@
         <v>162</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E3" s="89"/>
       <c r="F3" s="89" t="s">
@@ -3293,7 +3281,7 @@
         <v>82</v>
       </c>
       <c r="I3" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J3" s="89"/>
       <c r="K3" s="89"/>
@@ -3322,7 +3310,7 @@
         <v>82</v>
       </c>
       <c r="I4" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J4" s="89"/>
       <c r="K4" s="89"/>
@@ -3351,7 +3339,7 @@
         <v>82</v>
       </c>
       <c r="I5" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J5" s="89"/>
       <c r="K5" s="89"/>
@@ -3380,7 +3368,7 @@
         <v>82</v>
       </c>
       <c r="I6" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J6" s="89"/>
       <c r="K6" s="89"/>
@@ -3409,7 +3397,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J7" s="89"/>
       <c r="K7" s="89"/>
@@ -3438,7 +3426,7 @@
         <v>82</v>
       </c>
       <c r="I8" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J8" s="89"/>
       <c r="K8" s="89"/>
@@ -3467,7 +3455,7 @@
         <v>82</v>
       </c>
       <c r="I9" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J9" s="89"/>
       <c r="K9" s="89"/>
@@ -3496,7 +3484,7 @@
         <v>82</v>
       </c>
       <c r="I10" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J10" s="89"/>
       <c r="K10" s="89"/>
@@ -3509,10 +3497,10 @@
         <v>175</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D11" s="89" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E11" s="89"/>
       <c r="F11" s="89" t="s">
@@ -3525,7 +3513,7 @@
         <v>82</v>
       </c>
       <c r="I11" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J11" s="89"/>
       <c r="K11" s="89"/>
@@ -3535,13 +3523,13 @@
         <v>161</v>
       </c>
       <c r="B12" s="89" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C12" s="89" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D12" s="89" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89" t="s">
@@ -3554,7 +3542,7 @@
         <v>82</v>
       </c>
       <c r="I12" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J12" s="89"/>
       <c r="K12" s="89"/>
@@ -3564,7 +3552,7 @@
         <v>161</v>
       </c>
       <c r="B13" s="89" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C13" s="89" t="s">
         <v>165</v>
@@ -3583,7 +3571,7 @@
         <v>82</v>
       </c>
       <c r="I13" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J13" s="89"/>
       <c r="K13" s="89"/>
@@ -3593,13 +3581,13 @@
         <v>161</v>
       </c>
       <c r="B14" s="89" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C14" s="89" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D14" s="89" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E14" s="89"/>
       <c r="F14" s="89" t="s">
@@ -3612,7 +3600,7 @@
         <v>82</v>
       </c>
       <c r="I14" s="89" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J14" s="89"/>
       <c r="K14" s="89"/>
@@ -3622,26 +3610,26 @@
         <v>161</v>
       </c>
       <c r="B15" s="89" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C15" s="89" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D15" s="89" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E15" s="89"/>
       <c r="F15" s="89" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G15" s="89" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H15" s="89" t="s">
         <v>76</v>
       </c>
       <c r="I15" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="J15" s="89"/>
       <c r="K15" s="89"/>
@@ -3651,24 +3639,24 @@
         <v>161</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C16" s="89" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D16" s="89" t="s">
         <v>163</v>
       </c>
       <c r="E16" s="89"/>
       <c r="F16" s="89" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="G16" s="89"/>
       <c r="H16" s="89" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="I16" s="89" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J16" s="89"/>
       <c r="K16" s="89"/>
@@ -4233,10 +4221,10 @@
         <v>224</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D2" s="93" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4244,7 +4232,7 @@
       <c r="B3" s="115"/>
       <c r="C3" s="111"/>
       <c r="D3" s="93" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4255,10 +4243,10 @@
         <v>226</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D4" s="93" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4266,7 +4254,7 @@
       <c r="B5" s="113"/>
       <c r="C5" s="111"/>
       <c r="D5" s="93" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4277,10 +4265,10 @@
         <v>228</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D6" s="93" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4288,21 +4276,21 @@
         <v>229</v>
       </c>
       <c r="B7" s="83" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D7" s="93" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="97" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B8" s="91" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C8" s="90" t="s">
         <v>135</v>
@@ -4313,16 +4301,16 @@
     </row>
     <row r="9" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="80" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C9" s="95" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D9" s="82" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4335,16 +4323,16 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="80" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B11" s="80" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D11" s="93" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4352,7 +4340,7 @@
       <c r="B12" s="79"/>
       <c r="C12" s="84"/>
       <c r="D12" s="93" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4360,7 +4348,7 @@
       <c r="B13" s="79"/>
       <c r="C13" s="84"/>
       <c r="D13" s="93" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4368,7 +4356,7 @@
       <c r="B14" s="79"/>
       <c r="C14" s="84"/>
       <c r="D14" s="93" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4378,7 +4366,7 @@
         <v>230</v>
       </c>
       <c r="D15" s="93" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4386,7 +4374,7 @@
       <c r="B16" s="79"/>
       <c r="C16" s="79"/>
       <c r="D16" s="93" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -4396,7 +4384,7 @@
         <v>231</v>
       </c>
       <c r="D17" s="93" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4406,7 +4394,7 @@
         <v>232</v>
       </c>
       <c r="D18" s="93" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4414,7 +4402,7 @@
       <c r="B19" s="79"/>
       <c r="C19" s="79"/>
       <c r="D19" s="93" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4428,7 +4416,7 @@
         <v>235</v>
       </c>
       <c r="D20" s="93" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4436,7 +4424,7 @@
       <c r="B21" s="79"/>
       <c r="C21" s="84"/>
       <c r="D21" s="93" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4444,7 +4432,7 @@
       <c r="B22" s="79"/>
       <c r="C22" s="84"/>
       <c r="D22" s="93" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -4454,7 +4442,7 @@
         <v>236</v>
       </c>
       <c r="D23" s="93" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -4462,7 +4450,7 @@
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
       <c r="D24" s="93" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -4470,7 +4458,7 @@
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
       <c r="D25" s="93" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -4478,21 +4466,21 @@
       <c r="B26" s="79"/>
       <c r="C26" s="79"/>
       <c r="D26" s="93" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="39" x14ac:dyDescent="0.25">
       <c r="A27" s="80" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="D27" s="93" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -4509,16 +4497,16 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="85" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -4557,7 +4545,7 @@
         <v>243</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F1" s="50" t="s">
         <v>244</v>
@@ -4565,10 +4553,10 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C2">
         <v>12.34</v>
@@ -4577,18 +4565,18 @@
         <v>-16.95</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C3">
         <v>12.34</v>
@@ -4597,18 +4585,18 @@
         <v>-17.47</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C4">
         <v>12.51</v>
@@ -4617,18 +4605,18 @@
         <v>-17.61</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C5">
         <v>12.51</v>
@@ -4637,18 +4625,18 @@
         <v>-17.25</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B6" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C6">
         <v>12.67</v>
@@ -4657,18 +4645,18 @@
         <v>-17.2</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B7" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C7">
         <v>12.67</v>
@@ -4677,18 +4665,18 @@
         <v>-17.68</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B8" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C8">
         <v>12.84</v>
@@ -4697,18 +4685,18 @@
         <v>-17.68</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B9" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C9">
         <v>12.84</v>
@@ -4717,18 +4705,18 @@
         <v>-17.12</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B10" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C10">
         <v>13.01</v>
@@ -4737,18 +4725,18 @@
         <v>-17.05</v>
       </c>
       <c r="E10" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="F10" s="51" t="s">
         <v>569</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B11" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C11">
         <v>13.01</v>
@@ -4757,18 +4745,18 @@
         <v>-17.66</v>
       </c>
       <c r="E11" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="F11" s="51" t="s">
         <v>569</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B12" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C12">
         <v>13.17</v>
@@ -4777,18 +4765,18 @@
         <v>-17.62</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B13" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C13">
         <v>13.17</v>
@@ -4797,18 +4785,18 @@
         <v>-17.04</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B14" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C14">
         <v>13.34</v>
@@ -4817,18 +4805,18 @@
         <v>-17.03</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B15" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C15">
         <v>13.34</v>
@@ -4837,18 +4825,18 @@
         <v>-17.57</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B16" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C16">
         <v>13.51</v>
@@ -4857,18 +4845,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B17" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C17">
         <v>13.51</v>
@@ -4877,18 +4865,18 @@
         <v>-16.989999999999998</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B18" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C18">
         <v>13.67</v>
@@ -4897,18 +4885,18 @@
         <v>-17.02</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C19">
         <v>13.68</v>
@@ -4917,18 +4905,18 @@
         <v>-17.48</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B20" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C20">
         <v>13.84</v>
@@ -4937,18 +4925,18 @@
         <v>-17.48</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B21" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C21">
         <v>13.84</v>
@@ -4957,18 +4945,18 @@
         <v>-17.02</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B22" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C22">
         <v>14.01</v>
@@ -4977,18 +4965,18 @@
         <v>-17.05</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B23" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C23">
         <v>14.01</v>
@@ -4997,18 +4985,18 @@
         <v>-17.53</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B24" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C24">
         <v>14.18</v>
@@ -5017,18 +5005,18 @@
         <v>-17.55</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B25" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C25">
         <v>14.18</v>
@@ -5037,18 +5025,18 @@
         <v>-17.11</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B26" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C26">
         <v>14.34</v>
@@ -5057,18 +5045,18 @@
         <v>-17.14</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B27" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C27">
         <v>14.34</v>
@@ -5077,18 +5065,18 @@
         <v>-17.579999999999998</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B28" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C28">
         <v>14.51</v>
@@ -5097,18 +5085,18 @@
         <v>-17.63</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B29" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C29">
         <v>14.51</v>
@@ -5117,18 +5105,18 @@
         <v>-17.16</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B30" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C30">
         <v>14.68</v>
@@ -5137,18 +5125,18 @@
         <v>-17.48</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B31" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C31">
         <v>14.68</v>
@@ -5157,18 +5145,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B32" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C32">
         <v>14.84</v>
@@ -5177,18 +5165,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B33" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C33">
         <v>14.79</v>
@@ -5197,18 +5185,18 @@
         <v>-17.43</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B34" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C34">
         <v>14.86</v>
@@ -5217,18 +5205,18 @@
         <v>-17.28</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B35" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C35">
         <v>15.01</v>
@@ -5237,18 +5225,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B36" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C36">
         <v>15.12</v>
@@ -5257,18 +5245,18 @@
         <v>-17.36</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B37" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C37">
         <v>14.95</v>
@@ -5277,18 +5265,18 @@
         <v>-17.12</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B38" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C38">
         <v>15.09</v>
@@ -5297,18 +5285,18 @@
         <v>-17.02</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B39" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C39">
         <v>15.28</v>
@@ -5317,18 +5305,18 @@
         <v>-17.28</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B40" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C40">
         <v>15.45</v>
@@ -5337,18 +5325,18 @@
         <v>-17.239999999999998</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B41" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C41">
         <v>15.23</v>
@@ -5357,18 +5345,18 @@
         <v>-16.920000000000002</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B42" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C42">
         <v>15.38</v>
@@ -5377,18 +5365,18 @@
         <v>-16.84</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B43" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C43">
         <v>15.6</v>
@@ -5397,18 +5385,18 @@
         <v>-17.149999999999999</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B44" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C44">
         <v>15.75</v>
@@ -5417,18 +5405,18 @@
         <v>-17.079999999999998</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B45" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C45">
         <v>15.53</v>
@@ -5437,18 +5425,18 @@
         <v>-16.760000000000002</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B46" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C46">
         <v>15.67</v>
@@ -5457,18 +5445,18 @@
         <v>-16.670000000000002</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C47">
         <v>15.91</v>
@@ -5477,18 +5465,18 @@
         <v>-17</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B48" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C48">
         <v>16.05</v>
@@ -5497,18 +5485,18 @@
         <v>-16.97</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F48" s="51" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B49" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C49">
         <v>15.86</v>
@@ -5517,10 +5505,10 @@
         <v>-16.59</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -6475,7 +6463,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -6495,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>296</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6516,26 +6504,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -6578,62 +6550,62 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B2" s="6">
         <v>13</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B3" s="6">
         <v>25</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B4">
         <v>29</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -6680,7 +6652,7 @@
         <v>39</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>40</v>
@@ -6691,7 +6663,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>42</v>
@@ -6699,13 +6671,13 @@
     </row>
     <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -6789,19 +6761,19 @@
         <v>55</v>
       </c>
       <c r="G1" s="67" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H1" s="67" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I1" s="67" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="J1" s="67" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="K1" s="67" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L1" s="67" t="s">
         <v>56</v>
@@ -6813,12 +6785,12 @@
         <v>58</v>
       </c>
       <c r="O1" s="67" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B2" s="69" t="s">
         <v>59</v>
@@ -6853,7 +6825,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B3" s="69" t="s">
         <v>60</v>
@@ -6888,7 +6860,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B4" s="69" t="s">
         <v>61</v>
@@ -6921,7 +6893,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B5" s="69" t="s">
         <v>62</v>
@@ -6952,7 +6924,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="69" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>63</v>
@@ -6987,7 +6959,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B7" s="69" t="s">
         <v>64</v>
@@ -7028,7 +7000,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="69" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B8" s="69" t="s">
         <v>65</v>
@@ -7057,7 +7029,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="69" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B9" s="69" t="s">
         <v>66</v>
@@ -7092,7 +7064,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="69" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B10" s="69" t="s">
         <v>67</v>
@@ -7171,16 +7143,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>75</v>
@@ -7189,21 +7161,21 @@
         <v>76</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>79</v>
@@ -7217,16 +7189,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>75</v>
@@ -7240,16 +7212,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B5" s="101" t="s">
+        <v>472</v>
+      </c>
+      <c r="C5" s="101" t="s">
+        <v>473</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>477</v>
-      </c>
-      <c r="C5" s="101" t="s">
-        <v>478</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>482</v>
       </c>
       <c r="E5" s="101" t="s">
         <v>75</v>
@@ -7258,21 +7230,21 @@
         <v>76</v>
       </c>
       <c r="G5" s="101" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B6" s="101" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E6" s="101" t="s">
         <v>79</v>
@@ -7286,16 +7258,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>80</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>75</v>
@@ -7309,16 +7281,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="101" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>75</v>
@@ -7753,19 +7725,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D1" s="105" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7773,16 +7745,16 @@
         <v>3587</v>
       </c>
       <c r="B2" s="104" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C2" s="104" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7790,16 +7762,16 @@
         <v>3588</v>
       </c>
       <c r="B3" s="104" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C3" s="104" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7807,16 +7779,16 @@
         <v>3596</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C4" s="104" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7824,16 +7796,16 @@
         <v>3597</v>
       </c>
       <c r="B5" s="104" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7841,16 +7813,16 @@
         <v>3598</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C6" s="104" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7858,16 +7830,16 @@
         <v>3599</v>
       </c>
       <c r="B7" s="104" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C7" s="104" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7875,16 +7847,16 @@
         <v>3031</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C8" s="104" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7892,16 +7864,16 @@
         <v>3032</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C9" s="104" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7909,16 +7881,16 @@
         <v>3033</v>
       </c>
       <c r="B10" s="104" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C10" s="104" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7926,16 +7898,16 @@
         <v>3034</v>
       </c>
       <c r="B11" s="104" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C11" s="104" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7943,16 +7915,16 @@
         <v>3548</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C12" s="104" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7960,16 +7932,16 @@
         <v>3549</v>
       </c>
       <c r="B13" s="104" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C13" s="104" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7977,16 +7949,16 @@
         <v>3136</v>
       </c>
       <c r="B14" s="104" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C14" s="104" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -7994,16 +7966,16 @@
         <v>2105</v>
       </c>
       <c r="B15" s="104" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C15" s="104" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -8011,16 +7983,16 @@
         <v>2121</v>
       </c>
       <c r="B16" s="104" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -8028,16 +8000,16 @@
         <v>2133</v>
       </c>
       <c r="B17" s="104" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C17" s="104" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -8045,16 +8017,16 @@
         <v>2152</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C18" s="104" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -8062,16 +8034,16 @@
         <v>2154</v>
       </c>
       <c r="B19" s="104" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C19" s="104" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -8079,16 +8051,16 @@
         <v>2314</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C20" s="104" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -8096,16 +8068,16 @@
         <v>2375</v>
       </c>
       <c r="B21" s="104" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C21" s="104" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -8113,16 +8085,16 @@
         <v>2410</v>
       </c>
       <c r="B22" s="104" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -8130,16 +8102,16 @@
         <v>2502</v>
       </c>
       <c r="B23" s="104" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C23" s="104" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -8147,36 +8119,36 @@
         <v>7114</v>
       </c>
       <c r="B24" s="104" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C24" s="104" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B25" s="104" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C25" s="104"/>
       <c r="D25" s="21" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B26" s="104" t="s">
         <v>111</v>
@@ -8186,87 +8158,87 @@
         <v>62</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B27" s="104" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C27" s="104"/>
       <c r="D27" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="106" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B28" s="107" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C28" s="107"/>
       <c r="D28" s="108" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E28" s="106" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B29" s="104" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C29" s="104"/>
       <c r="D29" s="21" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B30" s="104" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C30" s="104"/>
       <c r="D30" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>425</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B31" s="104" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C31" s="104"/>
       <c r="D31" s="21" t="s">
         <v>85</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B32" s="104"/>
       <c r="C32" s="104"/>
@@ -8274,7 +8246,7 @@
         <v>84</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -8617,7 +8589,7 @@
         <v>105</v>
       </c>
       <c r="B20" s="101" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C20" s="101"/>
       <c r="D20" s="94"/>
@@ -8633,7 +8605,7 @@
         <v>105</v>
       </c>
       <c r="B21" s="101" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C21" s="101"/>
       <c r="D21" s="94"/>
@@ -8745,7 +8717,7 @@
         <v>120</v>
       </c>
       <c r="B28" s="101" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D28" s="94"/>
       <c r="E28" s="92" t="s">
@@ -8760,7 +8732,7 @@
         <v>120</v>
       </c>
       <c r="B29" s="101" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C29" s="94" t="s">
         <v>96</v>
@@ -8835,7 +8807,7 @@
         <v>119</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L1" s="38" t="s">
         <v>133</v>
@@ -8849,27 +8821,27 @@
         <v>135</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M2" s="43"/>
     </row>
@@ -8878,29 +8850,29 @@
         <v>136</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H3" s="18"/>
       <c r="J3" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M3" s="43"/>
     </row>
@@ -8909,10 +8881,10 @@
         <v>137</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="18"/>
@@ -8922,7 +8894,7 @@
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M4" s="43"/>
     </row>
@@ -8931,10 +8903,10 @@
         <v>138</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="18"/>
@@ -8944,7 +8916,7 @@
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M5" s="43"/>
     </row>
@@ -8953,29 +8925,29 @@
         <v>139</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M6" s="43"/>
     </row>
@@ -8984,10 +8956,10 @@
         <v>140</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="18"/>
@@ -8995,7 +8967,7 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
       <c r="I7" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="J7" s="18"/>
       <c r="M7" s="43"/>
@@ -9005,10 +8977,10 @@
         <v>141</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="18"/>
@@ -9018,7 +8990,7 @@
       <c r="I8" s="44"/>
       <c r="J8" s="18"/>
       <c r="L8" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M8" s="43"/>
     </row>
@@ -9027,26 +8999,26 @@
         <v>142</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
       <c r="M9" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -9054,10 +9026,10 @@
         <v>143</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="18"/>
@@ -9067,7 +9039,7 @@
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
       <c r="L10" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="M10" s="43"/>
     </row>
@@ -9076,10 +9048,10 @@
         <v>144</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="18"/>
@@ -9089,7 +9061,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="M11" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -9097,7 +9069,7 @@
         <v>145</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="47"/>
@@ -9113,10 +9085,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C13" s="77"/>
       <c r="D13" s="77"/>
@@ -9132,10 +9104,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B14" s="77" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C14" s="77"/>
       <c r="D14" s="77"/>
@@ -9245,26 +9217,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c01e712b-8f9b-4625-8219-31b20605feb3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2b166a80-dccc-42cc-be33-87bca7e0d87c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79A833CF10F444BBAB252802BF889FD" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9dbacadc2d62fa235a44cbd896f9338f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c01e712b-8f9b-4625-8219-31b20605feb3" xmlns:ns3="2b166a80-dccc-42cc-be33-87bca7e0d87c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1c5226f60b27328a0a64a71aebd5b96d" ns2:_="" ns3:_="">
     <xsd:import namespace="c01e712b-8f9b-4625-8219-31b20605feb3"/>
@@ -9507,27 +9459,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
-    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c01e712b-8f9b-4625-8219-31b20605feb3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2b166a80-dccc-42cc-be33-87bca7e0d87c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AAC0238-D15C-4B37-AA42-F7BBC8873F46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9544,4 +9496,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
+    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a5213\ownCloud\Nansen\Leg 5.1 2022\SailingOrder\_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB80BED-E2F8-4E1C-813C-708920FCA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12B078-4BD2-4EA1-A8DA-54A269B5C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18210" yWindow="4365" windowWidth="23025" windowHeight="9360" tabRatio="757" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="757" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="600">
   <si>
     <t>tab.name</t>
   </si>
@@ -1426,9 +1426,6 @@
     <t>To remain onboard</t>
   </si>
   <si>
-    <t>Leg 5.1 Senegal-Gambia (with calibration of  echosounders of DFN and parallell transects with R/V from Senegal)</t>
-  </si>
-  <si>
     <t>06/10/22</t>
   </si>
   <si>
@@ -1436,12 +1433,6 @@
   </si>
   <si>
     <t>Dakar</t>
-  </si>
-  <si>
-    <t>Leg 5.2 Mauritania (with paralell transects with R/V from Mauritania), + Cap Blanc-Cap Boujadour</t>
-  </si>
-  <si>
-    <t>Leg 5.3 cont. Cap Boujadour- Tanger, (with paralell transects with R/V from Morrocco)</t>
   </si>
   <si>
     <t>22/10/22</t>
@@ -1886,6 +1877,27 @@
   </si>
   <si>
     <t>North</t>
+  </si>
+  <si>
+    <t>Leg 5.1 Senegal-The Gambia</t>
+  </si>
+  <si>
+    <t>Additional activity</t>
+  </si>
+  <si>
+    <t>Leg 5.2 Mauritania + Cape Blanc-Cape Bojador</t>
+  </si>
+  <si>
+    <t>Leg 5.3 Cape Bojador- Tangier</t>
+  </si>
+  <si>
+    <t>calibration of echosounders of DFN and parallell transects with R/V from Senegal</t>
+  </si>
+  <si>
+    <t>paralell transects with R/V from Mauritania</t>
+  </si>
+  <si>
+    <t>paralell transects with R/V from Morocco</t>
   </si>
 </sst>
 </file>
@@ -4266,7 +4278,7 @@
       <c r="B5" s="113"/>
       <c r="C5" s="111"/>
       <c r="D5" s="93" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4291,10 +4303,10 @@
         <v>333</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D7" s="93" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4428,7 +4440,7 @@
         <v>235</v>
       </c>
       <c r="D20" s="93" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4436,7 +4448,7 @@
       <c r="B21" s="79"/>
       <c r="C21" s="84"/>
       <c r="D21" s="93" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4454,7 +4466,7 @@
         <v>236</v>
       </c>
       <c r="D23" s="93" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -4489,7 +4501,7 @@
         <v>320</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D27" s="93" t="s">
         <v>313</v>
@@ -4518,7 +4530,7 @@
         <v>309</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -4565,10 +4577,10 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C2">
         <v>12.34</v>
@@ -4577,18 +4589,18 @@
         <v>-16.95</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B3" t="s">
         <v>498</v>
-      </c>
-      <c r="B3" t="s">
-        <v>501</v>
       </c>
       <c r="C3">
         <v>12.34</v>
@@ -4597,18 +4609,18 @@
         <v>-17.47</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C4">
         <v>12.51</v>
@@ -4617,18 +4629,18 @@
         <v>-17.61</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C5">
         <v>12.51</v>
@@ -4637,18 +4649,18 @@
         <v>-17.25</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C6">
         <v>12.67</v>
@@ -4657,18 +4669,18 @@
         <v>-17.2</v>
       </c>
       <c r="E6" s="51" t="s">
+        <v>566</v>
+      </c>
+      <c r="F6" s="51" t="s">
         <v>569</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C7">
         <v>12.67</v>
@@ -4677,18 +4689,18 @@
         <v>-17.68</v>
       </c>
       <c r="E7" s="51" t="s">
+        <v>566</v>
+      </c>
+      <c r="F7" s="51" t="s">
         <v>569</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C8">
         <v>12.84</v>
@@ -4697,18 +4709,18 @@
         <v>-17.68</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B9" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C9">
         <v>12.84</v>
@@ -4717,18 +4729,18 @@
         <v>-17.12</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B10" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C10">
         <v>13.01</v>
@@ -4737,18 +4749,18 @@
         <v>-17.05</v>
       </c>
       <c r="E10" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B11" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C11">
         <v>13.01</v>
@@ -4757,18 +4769,18 @@
         <v>-17.66</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B12" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C12">
         <v>13.17</v>
@@ -4777,18 +4789,18 @@
         <v>-17.62</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B13" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C13">
         <v>13.17</v>
@@ -4797,18 +4809,18 @@
         <v>-17.04</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C14">
         <v>13.34</v>
@@ -4817,18 +4829,18 @@
         <v>-17.03</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>514</v>
+      </c>
+      <c r="B15" t="s">
         <v>517</v>
-      </c>
-      <c r="B15" t="s">
-        <v>520</v>
       </c>
       <c r="C15">
         <v>13.34</v>
@@ -4837,18 +4849,18 @@
         <v>-17.57</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B16" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C16">
         <v>13.51</v>
@@ -4857,18 +4869,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B17" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C17">
         <v>13.51</v>
@@ -4877,18 +4889,18 @@
         <v>-16.989999999999998</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B18" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C18">
         <v>13.67</v>
@@ -4897,18 +4909,18 @@
         <v>-17.02</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C19">
         <v>13.68</v>
@@ -4917,18 +4929,18 @@
         <v>-17.48</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B20" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C20">
         <v>13.84</v>
@@ -4937,18 +4949,18 @@
         <v>-17.48</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B21" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C21">
         <v>13.84</v>
@@ -4957,18 +4969,18 @@
         <v>-17.02</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B22" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C22">
         <v>14.01</v>
@@ -4977,18 +4989,18 @@
         <v>-17.05</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B23" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C23">
         <v>14.01</v>
@@ -4997,18 +5009,18 @@
         <v>-17.53</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B24" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C24">
         <v>14.18</v>
@@ -5017,18 +5029,18 @@
         <v>-17.55</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B25" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C25">
         <v>14.18</v>
@@ -5037,18 +5049,18 @@
         <v>-17.11</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B26" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C26">
         <v>14.34</v>
@@ -5057,18 +5069,18 @@
         <v>-17.14</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B27" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C27">
         <v>14.34</v>
@@ -5077,18 +5089,18 @@
         <v>-17.579999999999998</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B28" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C28">
         <v>14.51</v>
@@ -5097,18 +5109,18 @@
         <v>-17.63</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B29" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C29">
         <v>14.51</v>
@@ -5117,18 +5129,18 @@
         <v>-17.16</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B30" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C30">
         <v>14.68</v>
@@ -5137,18 +5149,18 @@
         <v>-17.48</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B31" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C31">
         <v>14.68</v>
@@ -5157,18 +5169,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B32" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C32">
         <v>14.84</v>
@@ -5177,18 +5189,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B33" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C33">
         <v>14.79</v>
@@ -5197,18 +5209,18 @@
         <v>-17.43</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B34" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C34">
         <v>14.86</v>
@@ -5217,18 +5229,18 @@
         <v>-17.28</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B35" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C35">
         <v>15.01</v>
@@ -5237,18 +5249,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B36" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C36">
         <v>15.12</v>
@@ -5257,18 +5269,18 @@
         <v>-17.36</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B37" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C37">
         <v>14.95</v>
@@ -5277,18 +5289,18 @@
         <v>-17.12</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B38" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C38">
         <v>15.09</v>
@@ -5297,18 +5309,18 @@
         <v>-17.02</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B39" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C39">
         <v>15.28</v>
@@ -5317,18 +5329,18 @@
         <v>-17.28</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B40" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C40">
         <v>15.45</v>
@@ -5337,18 +5349,18 @@
         <v>-17.239999999999998</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>546</v>
+      </c>
+      <c r="B41" t="s">
         <v>549</v>
-      </c>
-      <c r="B41" t="s">
-        <v>552</v>
       </c>
       <c r="C41">
         <v>15.23</v>
@@ -5357,18 +5369,18 @@
         <v>-16.920000000000002</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B42" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C42">
         <v>15.38</v>
@@ -5377,18 +5389,18 @@
         <v>-16.84</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B43" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C43">
         <v>15.6</v>
@@ -5397,18 +5409,18 @@
         <v>-17.149999999999999</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B44" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C44">
         <v>15.75</v>
@@ -5417,18 +5429,18 @@
         <v>-17.079999999999998</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B45" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C45">
         <v>15.53</v>
@@ -5437,18 +5449,18 @@
         <v>-16.760000000000002</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B46" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C46">
         <v>15.67</v>
@@ -5457,18 +5469,18 @@
         <v>-16.670000000000002</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C47">
         <v>15.91</v>
@@ -5477,18 +5489,18 @@
         <v>-17</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B48" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C48">
         <v>16.05</v>
@@ -5497,18 +5509,18 @@
         <v>-16.97</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F48" s="51" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B49" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C49">
         <v>15.86</v>
@@ -5517,10 +5529,10 @@
         <v>-16.59</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -6546,94 +6558,107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C2" s="6">
+        <v>13</v>
+      </c>
+      <c r="D2" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="B2" s="6">
-        <v>13</v>
-      </c>
-      <c r="C2" s="34" t="s">
+      <c r="E2" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="G2" s="32" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>595</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="C3" s="6">
+        <v>25</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="E3" s="34" t="s">
         <v>450</v>
       </c>
-      <c r="B3" s="6">
-        <v>25</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="F3" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="C4">
+        <v>29</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="E4" s="66" t="s">
         <v>452</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="F4" t="s">
         <v>453</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>449</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
-        <v>451</v>
-      </c>
-      <c r="B4">
-        <v>29</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>454</v>
-      </c>
-      <c r="D4" s="66" t="s">
-        <v>455</v>
-      </c>
-      <c r="E4" t="s">
-        <v>456</v>
-      </c>
-      <c r="F4" t="s">
-        <v>456</v>
+      <c r="G4" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -6789,19 +6814,19 @@
         <v>55</v>
       </c>
       <c r="G1" s="67" t="s">
+        <v>463</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>467</v>
+      </c>
+      <c r="I1" s="67" t="s">
+        <v>465</v>
+      </c>
+      <c r="J1" s="67" t="s">
         <v>466</v>
       </c>
-      <c r="H1" s="67" t="s">
-        <v>470</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>468</v>
-      </c>
-      <c r="J1" s="67" t="s">
-        <v>469</v>
-      </c>
       <c r="K1" s="67" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L1" s="67" t="s">
         <v>56</v>
@@ -6818,7 +6843,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B2" s="69" t="s">
         <v>59</v>
@@ -6853,7 +6878,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B3" s="69" t="s">
         <v>60</v>
@@ -6888,7 +6913,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B4" s="69" t="s">
         <v>61</v>
@@ -6921,7 +6946,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B5" s="69" t="s">
         <v>62</v>
@@ -6952,7 +6977,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="69" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B6" s="69" t="s">
         <v>63</v>
@@ -6987,7 +7012,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B7" s="69" t="s">
         <v>64</v>
@@ -7028,7 +7053,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="69" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B8" s="69" t="s">
         <v>65</v>
@@ -7057,7 +7082,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="69" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B9" s="69" t="s">
         <v>66</v>
@@ -7092,7 +7117,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="69" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B10" s="69" t="s">
         <v>67</v>
@@ -7171,16 +7196,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>75</v>
@@ -7189,21 +7214,21 @@
         <v>76</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>79</v>
@@ -7217,16 +7242,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>75</v>
@@ -7240,16 +7265,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B5" s="101" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C5" s="101" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E5" s="101" t="s">
         <v>75</v>
@@ -7258,21 +7283,21 @@
         <v>76</v>
       </c>
       <c r="G5" s="101" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B6" s="101" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E6" s="101" t="s">
         <v>79</v>
@@ -7286,16 +7311,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>80</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>75</v>
@@ -7309,16 +7334,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="101" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>75</v>
@@ -9245,6 +9270,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c01e712b-8f9b-4625-8219-31b20605feb3">
@@ -9253,15 +9287,6 @@
     <TaxCatchAll xmlns="2b166a80-dccc-42cc-be33-87bca7e0d87c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9508,6 +9533,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9515,14 +9548,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
     <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12B078-4BD2-4EA1-A8DA-54A269B5C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8607A1-0421-492B-9EDA-BE5C19F7CC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="757" firstSheet="7" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="757" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="606">
   <si>
     <t>tab.name</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Theme 1</t>
   </si>
   <si>
-    <t>Identification guide to ichthyoplankton in Southwest Africa</t>
-  </si>
-  <si>
     <t>Edoardo Mostarda (FAO), Stamatina Isari (IMR)</t>
   </si>
   <si>
@@ -178,12 +175,6 @@
     <t>Nikolaos Nikolioudakis (IMR)</t>
   </si>
   <si>
-    <t>Theme 3</t>
-  </si>
-  <si>
-    <t>Bjørn Erik Axelsen (IMR)</t>
-  </si>
-  <si>
     <t>Survey Name</t>
   </si>
   <si>
@@ -944,9 +935,6 @@
   </si>
   <si>
     <t>Leg 4.1 survey acoustic transects and strata in South-West Africa for small pelagic recruitment purposes.</t>
-  </si>
-  <si>
-    <t>Community structure of mesopelagic fish</t>
   </si>
   <si>
     <t>*Sardinella maderensis*</t>
@@ -1385,9 +1373,6 @@
   </si>
   <si>
     <t>Observer</t>
-  </si>
-  <si>
-    <t>Addressing population structure of shared pelagic stocks (*T. capensis*)</t>
   </si>
   <si>
     <t>horse mackerel for parasites analysis for stock identification.</t>
@@ -1898,6 +1883,39 @@
   </si>
   <si>
     <t>paralell transects with R/V from Morocco</t>
+  </si>
+  <si>
+    <t>Theme 6 </t>
+  </si>
+  <si>
+    <t>Bjørn Einar Grøsvik (IMR), Peter Kershaw (FAO consultant and GESAMP) </t>
+  </si>
+  <si>
+    <t>Theme 10</t>
+  </si>
+  <si>
+    <t>Theme 8</t>
+  </si>
+  <si>
+    <t>Marian Kjellevold (IMR)</t>
+  </si>
+  <si>
+    <t>Melissa Chierici (IMR)</t>
+  </si>
+  <si>
+    <t>Marine debris and microplastics: occurrence and impacts on marine ecosystems</t>
+  </si>
+  <si>
+    <t>Identification guide to ichthyoplankton in Northwest Africa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addressing population structure of shared pelagic stocks, Investigation of bias in echo sounder acoustic surveys using omni directional sonar </t>
+  </si>
+  <si>
+    <t>Future studies of nutrient profiles, contaminants and microplastics of sardinella and anchovy </t>
+  </si>
+  <si>
+    <t>Ocean acidification state and drivers in upwelling systems</t>
   </si>
 </sst>
 </file>
@@ -3093,7 +3111,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3125,7 +3143,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3133,7 +3151,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3141,7 +3159,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3149,7 +3167,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3173,7 +3191,7 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3181,7 +3199,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3189,7 +3207,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3217,470 +3235,470 @@
   <sheetData>
     <row r="1" spans="1:11" s="72" customFormat="1" ht="72" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="E1" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="F1" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="G1" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="74" t="s">
+      <c r="H1" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="74" t="s">
+      <c r="I1" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="J1" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="K1" s="74" t="s">
         <v>153</v>
-      </c>
-      <c r="I1" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="J1" s="74" t="s">
-        <v>155</v>
-      </c>
-      <c r="K1" s="74" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="89" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="89" t="s">
-        <v>367</v>
-      </c>
-      <c r="C2" s="89" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="89" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="89" t="s">
-        <v>160</v>
-      </c>
       <c r="F2" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G2" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H2" s="89" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I2" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J2" s="89"/>
       <c r="K2" s="89"/>
     </row>
     <row r="3" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B3" s="89" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D3" s="89" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E3" s="89"/>
       <c r="F3" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G3" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H3" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I3" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J3" s="89"/>
       <c r="K3" s="89"/>
     </row>
     <row r="4" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="89" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="89" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="89" t="s">
-        <v>164</v>
-      </c>
       <c r="C4" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E4" s="89"/>
       <c r="F4" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G4" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H4" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I4" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J4" s="89"/>
       <c r="K4" s="89"/>
     </row>
     <row r="5" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" s="89" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D5" s="89" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E5" s="89"/>
       <c r="F5" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H5" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I5" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J5" s="89"/>
       <c r="K5" s="89"/>
     </row>
     <row r="6" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C6" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E6" s="89"/>
       <c r="F6" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G6" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H6" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I6" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J6" s="89"/>
       <c r="K6" s="89"/>
     </row>
     <row r="7" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D7" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E7" s="89"/>
       <c r="F7" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G7" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H7" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I7" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J7" s="89"/>
       <c r="K7" s="89"/>
     </row>
     <row r="8" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B8" s="89" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D8" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E8" s="89"/>
       <c r="F8" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G8" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H8" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I8" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J8" s="89"/>
       <c r="K8" s="89"/>
     </row>
     <row r="9" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C9" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D9" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E9" s="89"/>
       <c r="F9" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H9" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I9" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J9" s="89"/>
       <c r="K9" s="89"/>
     </row>
     <row r="10" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B10" s="89" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D10" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E10" s="89"/>
       <c r="F10" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G10" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H10" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I10" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J10" s="89"/>
       <c r="K10" s="89"/>
     </row>
     <row r="11" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B11" s="89" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D11" s="89" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E11" s="89"/>
       <c r="F11" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H11" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I11" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J11" s="89"/>
       <c r="K11" s="89"/>
     </row>
     <row r="12" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B12" s="89" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" s="89" t="s">
+        <v>341</v>
+      </c>
+      <c r="D12" s="89" t="s">
         <v>342</v>
-      </c>
-      <c r="C12" s="89" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="89" t="s">
-        <v>346</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G12" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H12" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I12" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J12" s="89"/>
       <c r="K12" s="89"/>
     </row>
     <row r="13" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B13" s="89" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C13" s="89" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D13" s="89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E13" s="89"/>
       <c r="F13" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H13" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I13" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J13" s="89"/>
       <c r="K13" s="89"/>
     </row>
     <row r="14" spans="1:11" s="72" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B14" s="89" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C14" s="89" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D14" s="89" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E14" s="89"/>
       <c r="F14" s="89" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G14" s="89" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H14" s="89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I14" s="89" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J14" s="89"/>
       <c r="K14" s="89"/>
     </row>
     <row r="15" spans="1:11" s="72" customFormat="1" ht="72" x14ac:dyDescent="0.25">
       <c r="A15" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B15" s="89" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C15" s="89" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D15" s="89" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E15" s="89"/>
       <c r="F15" s="89" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G15" s="89" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H15" s="89" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I15" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="J15" s="89"/>
       <c r="K15" s="89"/>
     </row>
     <row r="16" spans="1:11" s="72" customFormat="1" ht="72" x14ac:dyDescent="0.25">
       <c r="A16" s="89" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C16" s="89" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D16" s="89" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E16" s="89"/>
       <c r="F16" s="89" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="G16" s="89"/>
       <c r="H16" s="89" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="I16" s="89" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J16" s="89"/>
       <c r="K16" s="89"/>
@@ -3706,114 +3724,114 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="65" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3841,7 +3859,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="109" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B1" s="109"/>
       <c r="C1" s="109"/>
@@ -3856,212 +3874,212 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4083,50 +4101,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4145,66 +4163,66 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -4225,30 +4243,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B1" s="78" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D1" s="78" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="114" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B2" s="114" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D2" s="93" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4256,21 +4274,21 @@
       <c r="B3" s="115"/>
       <c r="C3" s="111"/>
       <c r="D3" s="93" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="112" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B4" s="113" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D4" s="93" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4278,63 +4296,63 @@
       <c r="B5" s="113"/>
       <c r="C5" s="111"/>
       <c r="D5" s="93" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="79" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B6" s="79" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D6" s="93" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="80" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B7" s="83" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D7" s="93" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="97" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B8" s="91" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D8" s="93" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="80" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C9" s="95" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D9" s="82" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4342,21 +4360,21 @@
       <c r="B10" s="79"/>
       <c r="C10" s="84"/>
       <c r="D10" s="95" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="80" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B11" s="80" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D11" s="93" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4364,7 +4382,7 @@
       <c r="B12" s="79"/>
       <c r="C12" s="84"/>
       <c r="D12" s="93" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4372,7 +4390,7 @@
       <c r="B13" s="79"/>
       <c r="C13" s="84"/>
       <c r="D13" s="93" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4380,17 +4398,17 @@
       <c r="B14" s="79"/>
       <c r="C14" s="84"/>
       <c r="D14" s="93" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="86"/>
       <c r="B15" s="79"/>
       <c r="C15" s="80" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D15" s="93" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4398,27 +4416,27 @@
       <c r="B16" s="79"/>
       <c r="C16" s="79"/>
       <c r="D16" s="93" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="86"/>
       <c r="B17" s="79"/>
       <c r="C17" s="79" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D17" s="93" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="86"/>
       <c r="B18" s="79"/>
       <c r="C18" s="79" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D18" s="93" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4426,21 +4444,21 @@
       <c r="B19" s="79"/>
       <c r="C19" s="79"/>
       <c r="D19" s="93" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="80" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B20" s="80" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C20" s="85" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D20" s="93" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4448,7 +4466,7 @@
       <c r="B21" s="79"/>
       <c r="C21" s="84"/>
       <c r="D21" s="93" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4456,17 +4474,17 @@
       <c r="B22" s="79"/>
       <c r="C22" s="84"/>
       <c r="D22" s="93" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="79"/>
       <c r="B23" s="79"/>
       <c r="C23" s="79" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D23" s="93" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -4474,7 +4492,7 @@
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
       <c r="D24" s="93" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -4482,7 +4500,7 @@
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
       <c r="D25" s="93" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -4490,47 +4508,47 @@
       <c r="B26" s="79"/>
       <c r="C26" s="79"/>
       <c r="D26" s="93" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="39" x14ac:dyDescent="0.25">
       <c r="A27" s="80" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B27" s="88" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C27" s="96" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D27" s="93" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="80" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B28" s="80" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C28" s="80" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D28" s="80"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="85" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B29" s="85" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C29" s="87" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D29" s="93" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -4557,30 +4575,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="E1" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="F1" s="50" t="s">
         <v>241</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>328</v>
-      </c>
-      <c r="F1" s="50" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C2">
         <v>12.34</v>
@@ -4589,18 +4607,18 @@
         <v>-16.95</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B3" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C3">
         <v>12.34</v>
@@ -4609,18 +4627,18 @@
         <v>-17.47</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B4" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C4">
         <v>12.51</v>
@@ -4629,18 +4647,18 @@
         <v>-17.61</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B5" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C5">
         <v>12.51</v>
@@ -4649,18 +4667,18 @@
         <v>-17.25</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B6" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C6">
         <v>12.67</v>
@@ -4669,18 +4687,18 @@
         <v>-17.2</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B7" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C7">
         <v>12.67</v>
@@ -4689,18 +4707,18 @@
         <v>-17.68</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B8" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C8">
         <v>12.84</v>
@@ -4709,18 +4727,18 @@
         <v>-17.68</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B9" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C9">
         <v>12.84</v>
@@ -4729,18 +4747,18 @@
         <v>-17.12</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B10" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C10">
         <v>13.01</v>
@@ -4749,18 +4767,18 @@
         <v>-17.05</v>
       </c>
       <c r="E10" s="51" t="s">
+        <v>561</v>
+      </c>
+      <c r="F10" s="51" t="s">
         <v>566</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B11" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C11">
         <v>13.01</v>
@@ -4769,18 +4787,18 @@
         <v>-17.66</v>
       </c>
       <c r="E11" s="51" t="s">
+        <v>561</v>
+      </c>
+      <c r="F11" s="51" t="s">
         <v>566</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B12" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C12">
         <v>13.17</v>
@@ -4789,18 +4807,18 @@
         <v>-17.62</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B13" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C13">
         <v>13.17</v>
@@ -4809,18 +4827,18 @@
         <v>-17.04</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B14" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C14">
         <v>13.34</v>
@@ -4829,18 +4847,18 @@
         <v>-17.03</v>
       </c>
       <c r="E14" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B15" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C15">
         <v>13.34</v>
@@ -4849,18 +4867,18 @@
         <v>-17.57</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B16" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C16">
         <v>13.51</v>
@@ -4869,18 +4887,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E16" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B17" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C17">
         <v>13.51</v>
@@ -4889,18 +4907,18 @@
         <v>-16.989999999999998</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B18" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C18">
         <v>13.67</v>
@@ -4909,18 +4927,18 @@
         <v>-17.02</v>
       </c>
       <c r="E18" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B19" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C19">
         <v>13.68</v>
@@ -4929,18 +4947,18 @@
         <v>-17.48</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B20" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C20">
         <v>13.84</v>
@@ -4949,18 +4967,18 @@
         <v>-17.48</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B21" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C21">
         <v>13.84</v>
@@ -4969,18 +4987,18 @@
         <v>-17.02</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B22" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C22">
         <v>14.01</v>
@@ -4989,18 +5007,18 @@
         <v>-17.05</v>
       </c>
       <c r="E22" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B23" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C23">
         <v>14.01</v>
@@ -5009,18 +5027,18 @@
         <v>-17.53</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B24" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C24">
         <v>14.18</v>
@@ -5029,18 +5047,18 @@
         <v>-17.55</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B25" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C25">
         <v>14.18</v>
@@ -5049,18 +5067,18 @@
         <v>-17.11</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B26" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C26">
         <v>14.34</v>
@@ -5069,18 +5087,18 @@
         <v>-17.14</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B27" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C27">
         <v>14.34</v>
@@ -5089,18 +5107,18 @@
         <v>-17.579999999999998</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B28" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C28">
         <v>14.51</v>
@@ -5109,18 +5127,18 @@
         <v>-17.63</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B29" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C29">
         <v>14.51</v>
@@ -5129,18 +5147,18 @@
         <v>-17.16</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B30" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C30">
         <v>14.68</v>
@@ -5149,18 +5167,18 @@
         <v>-17.48</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B31" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C31">
         <v>14.68</v>
@@ -5169,18 +5187,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B32" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C32">
         <v>14.84</v>
@@ -5189,18 +5207,18 @@
         <v>-17.649999999999999</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B33" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C33">
         <v>14.79</v>
@@ -5209,18 +5227,18 @@
         <v>-17.43</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B34" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C34">
         <v>14.86</v>
@@ -5229,18 +5247,18 @@
         <v>-17.28</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B35" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C35">
         <v>15.01</v>
@@ -5249,18 +5267,18 @@
         <v>-17.489999999999998</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B36" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C36">
         <v>15.12</v>
@@ -5269,18 +5287,18 @@
         <v>-17.36</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B37" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C37">
         <v>14.95</v>
@@ -5289,18 +5307,18 @@
         <v>-17.12</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B38" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C38">
         <v>15.09</v>
@@ -5309,18 +5327,18 @@
         <v>-17.02</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B39" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C39">
         <v>15.28</v>
@@ -5329,18 +5347,18 @@
         <v>-17.28</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B40" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C40">
         <v>15.45</v>
@@ -5349,18 +5367,18 @@
         <v>-17.239999999999998</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B41" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C41">
         <v>15.23</v>
@@ -5369,18 +5387,18 @@
         <v>-16.920000000000002</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B42" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C42">
         <v>15.38</v>
@@ -5389,18 +5407,18 @@
         <v>-16.84</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B43" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C43">
         <v>15.6</v>
@@ -5409,18 +5427,18 @@
         <v>-17.149999999999999</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B44" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C44">
         <v>15.75</v>
@@ -5429,18 +5447,18 @@
         <v>-17.079999999999998</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B45" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C45">
         <v>15.53</v>
@@ -5449,18 +5467,18 @@
         <v>-16.760000000000002</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B46" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C46">
         <v>15.67</v>
@@ -5469,18 +5487,18 @@
         <v>-16.670000000000002</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B47" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C47">
         <v>15.91</v>
@@ -5489,18 +5507,18 @@
         <v>-17</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B48" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C48">
         <v>16.05</v>
@@ -5509,18 +5527,18 @@
         <v>-16.97</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F48" s="51" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B49" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C49">
         <v>15.86</v>
@@ -5529,10 +5547,10 @@
         <v>-16.59</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -5554,45 +5572,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C1" s="52" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E1" s="53" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I1" s="52" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J1" s="53" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K1" s="52" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B2" s="54">
         <v>1</v>
@@ -5601,7 +5619,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E2" s="54">
         <v>28</v>
@@ -5610,7 +5628,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H2" s="54">
         <v>51</v>
@@ -5619,7 +5637,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="58" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K2" s="59">
         <v>73</v>
@@ -5794,7 +5812,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H8" s="54">
         <v>57</v>
@@ -5894,7 +5912,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B12" s="54">
         <v>11</v>
@@ -5929,7 +5947,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E13" s="54">
         <v>39</v>
@@ -5964,7 +5982,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H14" s="54">
         <v>63</v>
@@ -6160,7 +6178,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B22" s="54">
         <v>21</v>
@@ -6321,162 +6339,162 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -6507,7 +6525,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6528,18 +6546,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6547,7 +6565,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -6571,94 +6589,94 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C2" s="6">
         <v>13</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C3" s="6">
         <v>25</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C4">
         <v>29</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="F4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -6670,7 +6688,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -6694,54 +6712,66 @@
         <v>36</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>41</v>
+        <v>595</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>297</v>
+        <v>601</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>42</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>337</v>
+        <v>598</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>338</v>
+        <v>604</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+        <v>599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="A7" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
@@ -6764,9 +6794,14 @@
       <c r="C11" s="16"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6796,57 +6831,57 @@
   <sheetData>
     <row r="1" spans="1:15" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="E1" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="F1" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="G1" s="67" t="s">
+        <v>458</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>462</v>
+      </c>
+      <c r="I1" s="67" t="s">
+        <v>460</v>
+      </c>
+      <c r="J1" s="67" t="s">
+        <v>461</v>
+      </c>
+      <c r="K1" s="67" t="s">
+        <v>459</v>
+      </c>
+      <c r="L1" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="M1" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="N1" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="67" t="s">
-        <v>463</v>
-      </c>
-      <c r="H1" s="67" t="s">
-        <v>467</v>
-      </c>
-      <c r="I1" s="67" t="s">
-        <v>465</v>
-      </c>
-      <c r="J1" s="67" t="s">
-        <v>466</v>
-      </c>
-      <c r="K1" s="67" t="s">
-        <v>464</v>
-      </c>
-      <c r="L1" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="M1" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="N1" s="68" t="s">
-        <v>58</v>
-      </c>
       <c r="O1" s="67" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B2" s="69" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" s="36">
         <v>1</v>
@@ -6878,10 +6913,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C3" s="36">
         <v>1</v>
@@ -6913,10 +6948,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -6946,10 +6981,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B5" s="69" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
@@ -6977,10 +7012,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="69" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -7012,10 +7047,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" s="36">
         <v>11</v>
@@ -7053,10 +7088,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="69" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B8" s="69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -7082,10 +7117,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="69" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" s="36">
         <v>2</v>
@@ -7117,10 +7152,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="69" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C10" s="36">
         <v>4</v>
@@ -7173,186 +7208,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="F1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B5" s="101" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="101" t="s">
+        <v>470</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C5" s="101" t="s">
-        <v>475</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>479</v>
-      </c>
       <c r="E5" s="101" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F5" s="101" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G5" s="101" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B6" s="101" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E6" s="101" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F6" s="101" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" s="101" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="101" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7778,19 +7813,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D1" s="105" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7798,16 +7833,16 @@
         <v>3587</v>
       </c>
       <c r="B2" s="104" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C2" s="104" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7815,16 +7850,16 @@
         <v>3588</v>
       </c>
       <c r="B3" s="104" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C3" s="104" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7832,16 +7867,16 @@
         <v>3596</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C4" s="104" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7849,16 +7884,16 @@
         <v>3597</v>
       </c>
       <c r="B5" s="104" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7866,16 +7901,16 @@
         <v>3598</v>
       </c>
       <c r="B6" s="104" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C6" s="104" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7883,16 +7918,16 @@
         <v>3599</v>
       </c>
       <c r="B7" s="104" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C7" s="104" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7900,16 +7935,16 @@
         <v>3031</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C8" s="104" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7917,16 +7952,16 @@
         <v>3032</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C9" s="104" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7934,16 +7969,16 @@
         <v>3033</v>
       </c>
       <c r="B10" s="104" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C10" s="104" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7951,16 +7986,16 @@
         <v>3034</v>
       </c>
       <c r="B11" s="104" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C11" s="104" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7968,16 +8003,16 @@
         <v>3548</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C12" s="104" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7985,16 +8020,16 @@
         <v>3549</v>
       </c>
       <c r="B13" s="104" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C13" s="104" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -8002,16 +8037,16 @@
         <v>3136</v>
       </c>
       <c r="B14" s="104" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C14" s="104" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -8019,16 +8054,16 @@
         <v>2105</v>
       </c>
       <c r="B15" s="104" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C15" s="104" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -8036,16 +8071,16 @@
         <v>2121</v>
       </c>
       <c r="B16" s="104" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -8053,16 +8088,16 @@
         <v>2133</v>
       </c>
       <c r="B17" s="104" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C17" s="104" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -8070,16 +8105,16 @@
         <v>2152</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C18" s="104" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -8087,16 +8122,16 @@
         <v>2154</v>
       </c>
       <c r="B19" s="104" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C19" s="104" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -8104,16 +8139,16 @@
         <v>2314</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C20" s="104" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -8121,16 +8156,16 @@
         <v>2375</v>
       </c>
       <c r="B21" s="104" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C21" s="104" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -8138,16 +8173,16 @@
         <v>2410</v>
       </c>
       <c r="B22" s="104" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -8155,16 +8190,16 @@
         <v>2502</v>
       </c>
       <c r="B23" s="104" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C23" s="104" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -8172,134 +8207,134 @@
         <v>7114</v>
       </c>
       <c r="B24" s="104" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C24" s="104" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B25" s="104" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C25" s="104"/>
       <c r="D25" s="21" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B26" s="104" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C26" s="104"/>
       <c r="D26" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B27" s="104" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C27" s="104"/>
       <c r="D27" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="106" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B28" s="107" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C28" s="107"/>
       <c r="D28" s="108" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E28" s="106" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B29" s="104" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C29" s="104"/>
       <c r="D29" s="21" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B30" s="104" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C30" s="104"/>
       <c r="D30" s="21" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B31" s="104" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C31" s="104"/>
       <c r="D31" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B32" s="104"/>
       <c r="C32" s="104"/>
       <c r="D32" s="21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -8325,39 +8360,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D2" s="94"/>
       <c r="E2" s="94"/>
@@ -8367,61 +8402,61 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="101" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="101" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" s="101" t="s">
-        <v>97</v>
       </c>
       <c r="C3" s="94"/>
       <c r="D3" s="94"/>
       <c r="E3" s="94"/>
       <c r="F3" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G3" s="94"/>
       <c r="H3" s="94"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" s="94"/>
       <c r="D4" s="94"/>
       <c r="E4" s="94"/>
       <c r="F4" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" s="94"/>
       <c r="H4" s="94"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B5" s="101" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" s="94"/>
       <c r="D5" s="94"/>
       <c r="E5" s="94"/>
       <c r="F5" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G5" s="94"/>
       <c r="H5" s="94"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B6" s="101" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D6" s="94"/>
       <c r="E6" s="94"/>
@@ -8431,95 +8466,95 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B7" s="101" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="94"/>
       <c r="D7" s="94"/>
       <c r="E7" s="94"/>
       <c r="F7" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G7" s="94"/>
       <c r="H7" s="94"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B8" s="101" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="94"/>
       <c r="D8" s="94"/>
       <c r="E8" s="94"/>
       <c r="F8" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G8" s="94"/>
       <c r="H8" s="94"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B9" s="101" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="94"/>
       <c r="D9" s="94"/>
       <c r="E9" s="94"/>
       <c r="F9" s="103" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G9" s="94"/>
       <c r="H9" s="94"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="101" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B10" s="101" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C10" s="94"/>
       <c r="D10" s="94"/>
       <c r="E10" s="101"/>
       <c r="F10" s="103" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G10" s="94"/>
       <c r="H10" s="94"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B11" s="101" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C11" s="94"/>
       <c r="D11" s="94"/>
       <c r="E11" s="94"/>
       <c r="F11" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G11" s="94"/>
       <c r="H11" s="94"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B12" s="101" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C12" s="94"/>
       <c r="D12" s="94"/>
       <c r="E12" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F12" s="94"/>
       <c r="G12" s="94"/>
@@ -8527,15 +8562,15 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="101" t="s">
         <v>105</v>
-      </c>
-      <c r="B13" s="101" t="s">
-        <v>108</v>
       </c>
       <c r="C13" s="94"/>
       <c r="D13" s="94"/>
       <c r="E13" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F13" s="94"/>
       <c r="G13" s="94"/>
@@ -8543,15 +8578,15 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B14" s="101" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C14" s="94"/>
       <c r="D14" s="94"/>
       <c r="E14" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F14" s="94"/>
       <c r="G14" s="94"/>
@@ -8559,31 +8594,31 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B15" s="101" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C15" s="94"/>
       <c r="D15" s="94"/>
       <c r="E15" s="94"/>
       <c r="F15" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G15" s="94"/>
       <c r="H15" s="94"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B16" s="101" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C16" s="94"/>
       <c r="D16" s="94"/>
       <c r="E16" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F16" s="94"/>
       <c r="G16" s="94"/>
@@ -8591,93 +8626,93 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B17" s="101" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C17" s="94"/>
       <c r="D17" s="94"/>
       <c r="E17" s="94"/>
       <c r="F17" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G17" s="94"/>
       <c r="H17" s="94"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B18" s="101" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C18" s="101"/>
       <c r="D18" s="94"/>
       <c r="E18" s="94"/>
       <c r="F18" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G18" s="94"/>
       <c r="H18" s="94"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B19" s="101" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C19" s="101"/>
       <c r="D19" s="94"/>
       <c r="E19" s="94"/>
       <c r="F19" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G19" s="94"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B20" s="101" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C20" s="101"/>
       <c r="D20" s="94"/>
       <c r="E20" s="94"/>
       <c r="F20" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G20" s="94"/>
       <c r="H20" s="94"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="101" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B21" s="101" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C21" s="101"/>
       <c r="D21" s="94"/>
       <c r="E21" s="94"/>
       <c r="F21" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21" s="94"/>
       <c r="H21" s="94"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="101" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B22" s="101" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D22" s="94"/>
       <c r="E22" s="94"/>
@@ -8687,94 +8722,94 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="101" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B23" s="101" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C23" s="94"/>
       <c r="D23" s="94"/>
       <c r="E23" s="94"/>
       <c r="F23" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G23" s="94"/>
       <c r="H23" s="94"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="101" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B24" s="101" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" s="94"/>
       <c r="D24" s="101"/>
       <c r="E24" s="94"/>
       <c r="F24" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G24" s="94"/>
       <c r="H24" s="94"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="101" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B25" s="101" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C25" s="94"/>
       <c r="D25" s="94"/>
       <c r="E25" s="94"/>
       <c r="F25" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G25" s="94"/>
       <c r="H25" s="94"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="101" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B26" s="101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C26" s="94"/>
       <c r="D26" s="94"/>
       <c r="E26" s="94"/>
       <c r="F26" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G26" s="94"/>
       <c r="H26" s="94"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="101" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B27" s="101" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C27" s="94"/>
       <c r="D27" s="94"/>
       <c r="E27" s="94"/>
       <c r="F27" s="92" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G27" s="94"/>
       <c r="H27" s="94"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="101" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B28" s="101" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D28" s="94"/>
       <c r="E28" s="92" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F28" s="101"/>
       <c r="G28" s="94"/>
@@ -8782,13 +8817,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="101" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B29" s="101" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D29" s="94"/>
       <c r="E29" s="94"/>
@@ -8798,15 +8833,15 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="101" t="s">
         <v>120</v>
-      </c>
-      <c r="B30" s="101" t="s">
-        <v>123</v>
       </c>
       <c r="C30" s="101"/>
       <c r="D30" s="101"/>
       <c r="E30" s="101" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F30" s="101"/>
       <c r="G30" s="101"/>
@@ -8830,114 +8865,114 @@
   <sheetData>
     <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="E1" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="F1" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="G1" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="H1" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="I1" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="J1" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="L1" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="M1" s="39" t="s">
         <v>131</v>
-      </c>
-      <c r="I1" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="J1" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="L1" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H2" s="18"/>
       <c r="J2" s="18"/>
       <c r="K2" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H3" s="18"/>
       <c r="J3" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M3" s="43"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="18"/>
@@ -8947,19 +8982,19 @@
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M4" s="43"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="18"/>
@@ -8969,50 +9004,50 @@
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
       <c r="L5" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M5" s="43"/>
     </row>
     <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M6" s="43"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="18"/>
@@ -9020,20 +9055,20 @@
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
       <c r="I7" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J7" s="18"/>
       <c r="M7" s="43"/>
     </row>
     <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="18"/>
@@ -9043,46 +9078,46 @@
       <c r="I8" s="44"/>
       <c r="J8" s="18"/>
       <c r="L8" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M8" s="43"/>
     </row>
     <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
       <c r="M9" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="18"/>
@@ -9092,19 +9127,19 @@
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
       <c r="L10" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M10" s="43"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="18"/>
@@ -9114,15 +9149,15 @@
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="M11" s="42" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="46" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="47"/>
@@ -9138,10 +9173,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B13" s="77" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C13" s="77"/>
       <c r="D13" s="77"/>
@@ -9157,10 +9192,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B14" s="77" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C14" s="77"/>
       <c r="D14" s="77"/>
@@ -9270,26 +9305,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c01e712b-8f9b-4625-8219-31b20605feb3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2b166a80-dccc-42cc-be33-87bca7e0d87c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79A833CF10F444BBAB252802BF889FD" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9dbacadc2d62fa235a44cbd896f9338f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c01e712b-8f9b-4625-8219-31b20605feb3" xmlns:ns3="2b166a80-dccc-42cc-be33-87bca7e0d87c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1c5226f60b27328a0a64a71aebd5b96d" ns2:_="" ns3:_="">
     <xsd:import namespace="c01e712b-8f9b-4625-8219-31b20605feb3"/>
@@ -9532,10 +9547,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c01e712b-8f9b-4625-8219-31b20605feb3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2b166a80-dccc-42cc-be33-87bca7e0d87c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AAC0238-D15C-4B37-AA42-F7BBC8873F46}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
+    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9553,20 +9599,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AAC0238-D15C-4B37-AA42-F7BBC8873F46}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6570D26-28E5-4B10-84F9-A044851469F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
-    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\SailingOrdersDFN\_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58AB05C-62EE-4A92-A2BA-F69A87E8B47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E99E6C-5CD4-4057-82AE-7446435D7900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="757" firstSheet="4" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" tabRatio="757" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="426">
   <si>
     <t>tab.name</t>
   </si>
@@ -441,33 +441,6 @@
     <t>*Engraulis encrasicolus*</t>
   </si>
   <si>
-    <t>*Etrumeus whiteheadi*</t>
-  </si>
-  <si>
-    <t>*Lampanyctodes hectoris*</t>
-  </si>
-  <si>
-    <t>*Maurolicus walvisensis*</t>
-  </si>
-  <si>
-    <t>*Sardinops sagax*</t>
-  </si>
-  <si>
-    <t>*Scomber japonicus*</t>
-  </si>
-  <si>
-    <t>*Sufflogobius bibarbatus*</t>
-  </si>
-  <si>
-    <t>*Trachurus capensis*</t>
-  </si>
-  <si>
-    <t>Other mesopelagics</t>
-  </si>
-  <si>
-    <t>Jellyfish</t>
-  </si>
-  <si>
     <t>All remaining species caught</t>
   </si>
   <si>
@@ -537,28 +510,7 @@
     <t>Frozen (&gt;20 cm length)</t>
   </si>
   <si>
-    <t>sardine, anchovy and round herring for assessment of their anthropogenic pollutant (herbicides, pharmaceuticals) levels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frozen </t>
-  </si>
-  <si>
-    <t>chub mackerel for collection of meristic information for stock/species identification.</t>
-  </si>
-  <si>
     <t>Road</t>
-  </si>
-  <si>
-    <t>Hector’s lanternfish and lightfish for basic biology studies.</t>
-  </si>
-  <si>
-    <t>uncommon and/or unidentified mesopelagic fish species for basic biology studies.</t>
-  </si>
-  <si>
-    <t>pelagic gobies for basic biology studies.</t>
-  </si>
-  <si>
-    <t>jellyfish (Chrysaora and Aequorea) tissue for genetic analysis</t>
   </si>
   <si>
     <t>Stage</t>
@@ -933,30 +885,12 @@
     <t>Vials</t>
   </si>
   <si>
-    <t>jellyfish (Chrysaora and Aequorea)</t>
-  </si>
-  <si>
-    <t>Jars</t>
-  </si>
-  <si>
-    <t>96% ethanol for genetics</t>
-  </si>
-  <si>
-    <t>Whole organism if in good condition</t>
-  </si>
-  <si>
-    <t>4% formaldehyde solution</t>
-  </si>
-  <si>
     <t>pCO2</t>
   </si>
   <si>
     <t>Chlorophyll *a*</t>
   </si>
   <si>
-    <t>Peter Psomadakis, Peter.Psomadakis@fao.org</t>
-  </si>
-  <si>
     <t>Allocation of acoustic densities to species groups.</t>
   </si>
   <si>
@@ -1198,42 +1132,6 @@
   </si>
   <si>
     <t>Observer</t>
-  </si>
-  <si>
-    <t>horse mackerel for parasites analysis for stock identification.</t>
-  </si>
-  <si>
-    <t>horse mackerel otoliths for stock identification.</t>
-  </si>
-  <si>
-    <t>vials</t>
-  </si>
-  <si>
-    <t>horse mackerel fin clips for genetic analysis for stock identification.</t>
-  </si>
-  <si>
-    <t>fin-clips in vials</t>
-  </si>
-  <si>
-    <t>Bergen</t>
-  </si>
-  <si>
-    <t>Air</t>
-  </si>
-  <si>
-    <t>Nikolaos Nikolioudakis, nikolaos.nikolioudakis@hi.no</t>
-  </si>
-  <si>
-    <t>FAO</t>
-  </si>
-  <si>
-    <t>unidentified taxa - Taxonomy</t>
-  </si>
-  <si>
-    <t>Whole individual</t>
-  </si>
-  <si>
-    <t>To remain onboard</t>
   </si>
   <si>
     <t>06/10/22</t>
@@ -1425,28 +1323,55 @@
     <t>Ocean acidification state and drivers in upwelling systems</t>
   </si>
   <si>
+    <t>FAO (External experts)</t>
+  </si>
+  <si>
+    <t>Total Leg 5.1</t>
+  </si>
+  <si>
+    <t>Total Leg 5.2</t>
+  </si>
+  <si>
+    <t>Total Leg 5.3</t>
+  </si>
+  <si>
+    <t>Dave Boyer</t>
+  </si>
+  <si>
+    <t>Jens-Otto Krakstad</t>
+  </si>
+  <si>
+    <t>Instrument Engineer/Plankton Team leader</t>
+  </si>
+  <si>
     <t>Position (laboratory)</t>
   </si>
   <si>
-    <t>FAO (External experts)</t>
-  </si>
-  <si>
-    <t>Total Leg 5.1</t>
-  </si>
-  <si>
-    <t>Total Leg 5.2</t>
-  </si>
-  <si>
-    <t>Total Leg 5.3</t>
-  </si>
-  <si>
-    <t>Dave Boyer</t>
-  </si>
-  <si>
-    <t>Jens-Otto Krakstad</t>
-  </si>
-  <si>
-    <t>Instrument Engineer/Plankton Team leader</t>
+    <t>*Sardinella aurita*</t>
+  </si>
+  <si>
+    <t>*Sardinella maderensis*</t>
+  </si>
+  <si>
+    <t>*Scomber colias*</t>
+  </si>
+  <si>
+    <t>*Trachurus trachurus*</t>
+  </si>
+  <si>
+    <t>*Trachurus trecae*</t>
+  </si>
+  <si>
+    <t>*Decapterous ronchus*</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>*Macroramphosus gracilis*</t>
+  </si>
+  <si>
+    <t>*Trachurus picturatus*</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1630,6 +1555,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1873,7 +1805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1956,9 +1888,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2035,15 +1964,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
@@ -2067,17 +1987,31 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2403,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2418,7 +2352,7 @@
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2435,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2443,7 +2377,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -2451,7 +2385,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2459,7 +2393,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2483,7 +2417,7 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2491,7 +2425,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2499,7 +2433,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -2525,475 +2459,301 @@
     <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="44" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:11" s="43" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="K1" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="46" t="s">
+    </row>
+    <row r="2" spans="1:11" s="43" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="B2" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="D2" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="E2" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="F2" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+    </row>
+    <row r="3" spans="1:11" s="43" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="B3" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="C3" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+    </row>
+    <row r="4" spans="1:11" s="43" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="K1" s="46" t="s">
+      <c r="E4" s="55"/>
+      <c r="F4" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+    </row>
+    <row r="5" spans="1:11" s="43" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>308</v>
-      </c>
-      <c r="C2" s="56" t="s">
+      <c r="D5" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="E5" s="55"/>
+      <c r="F5" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>307</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>282</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" s="56" t="s">
+      <c r="H5" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-    </row>
-    <row r="4" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-    </row>
-    <row r="5" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-    </row>
-    <row r="6" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-    </row>
-    <row r="7" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-    </row>
-    <row r="8" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-    </row>
-    <row r="9" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B9" s="56" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H9" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-    </row>
-    <row r="10" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-    </row>
-    <row r="11" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>284</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H11" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-    </row>
-    <row r="12" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H12" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-    </row>
-    <row r="13" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>372</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H13" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-    </row>
-    <row r="14" spans="1:11" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="56" t="s">
-        <v>373</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>374</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>281</v>
-      </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="H14" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="56" t="s">
-        <v>301</v>
-      </c>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-    </row>
-    <row r="15" spans="1:11" s="44" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>375</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>376</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56" t="s">
-        <v>377</v>
-      </c>
-      <c r="G15" s="56" t="s">
-        <v>378</v>
-      </c>
-      <c r="H15" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="56" t="s">
-        <v>379</v>
-      </c>
-      <c r="J15" s="56"/>
-      <c r="K15" s="56"/>
-    </row>
-    <row r="16" spans="1:11" s="44" customFormat="1" ht="72" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="56" t="s">
-        <v>381</v>
-      </c>
-      <c r="C16" s="56" t="s">
-        <v>382</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56" t="s">
-        <v>383</v>
-      </c>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56" t="s">
-        <v>380</v>
-      </c>
-      <c r="I16" s="56" t="s">
-        <v>290</v>
-      </c>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
+      <c r="I5" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+    </row>
+    <row r="6" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+    </row>
+    <row r="7" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+    </row>
+    <row r="8" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+    </row>
+    <row r="9" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+    </row>
+    <row r="10" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+    </row>
+    <row r="11" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+    </row>
+    <row r="12" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+    </row>
+    <row r="13" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+    </row>
+    <row r="14" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+    </row>
+    <row r="15" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+    </row>
+    <row r="16" spans="1:11" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="23"/>
@@ -3016,114 +2776,114 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="3" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="40" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="B6" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="40" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="B7" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3142,50 +2902,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3204,66 +2964,66 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3283,313 +3043,313 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="87" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="88"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="68" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="85" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="84" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="85"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="68" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="79" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>384</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="79" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>281</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="49"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="76" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="78" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="49"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="68" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="52"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="68" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="68" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="68" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="52"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="68" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="49"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="68" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="49"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="68" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="49"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="D23" s="68" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="68" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="57" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="57" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="39" x14ac:dyDescent="0.25">
+      <c r="A27" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>390</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="B28" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="C28" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="83" t="s">
-        <v>218</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>270</v>
-      </c>
-      <c r="D2" s="69" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="69" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="B4" s="83" t="s">
-        <v>220</v>
-      </c>
-      <c r="C4" s="84" t="s">
-        <v>271</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="69" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>222</v>
-      </c>
-      <c r="C6" s="86" t="s">
-        <v>272</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="B7" s="87" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="88" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="69" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="85" t="s">
+      <c r="D28" s="50"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="B29" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="C9" s="89" t="s">
-        <v>303</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="80" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="B11" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="82" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" s="69" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="69" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="53"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="69" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="53"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="69" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="53"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="53"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="53"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70" t="s">
-        <v>225</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="53"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70" t="s">
-        <v>226</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="53"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="69" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="B20" s="70" t="s">
-        <v>228</v>
-      </c>
-      <c r="C20" s="81" t="s">
-        <v>229</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="69" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70" t="s">
-        <v>230</v>
-      </c>
-      <c r="D23" s="69" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="69" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="58" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="58" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="39" x14ac:dyDescent="0.25">
-      <c r="A27" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>262</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>424</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="51"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>276</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>251</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>423</v>
+      <c r="C29" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -3628,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3640,7 +3400,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -3649,18 +3409,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3668,7 +3428,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3695,7 +3455,7 @@
         <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>41</v>
@@ -3715,71 +3475,71 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="C2" s="6">
         <v>13</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="C3" s="6">
         <v>25</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="C4">
         <v>29</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>390</v>
+        <v>355</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>356</v>
       </c>
       <c r="F4" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="G4" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3575,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>37</v>
@@ -3826,7 +3586,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -3834,46 +3594,46 @@
     </row>
     <row r="4" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>437</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3937,7 +3697,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>48</v>
@@ -3952,19 +3712,19 @@
         <v>51</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>52</v>
@@ -3973,301 +3733,301 @@
         <v>53</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="74">
+      <c r="C2" s="70">
         <v>1</v>
       </c>
       <c r="D2" s="27">
         <v>1</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="63">
         <v>1</v>
       </c>
-      <c r="F2" s="76" t="str">
+      <c r="F2" s="72" t="str">
         <f>IF(D2&gt;0, IF(D2-E2=0,"",D2-E2), IF(E2&gt;0,E2,""))</f>
         <v/>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="76" t="str">
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="72" t="str">
         <f t="shared" ref="L2:L10" si="0">IF(SUM(G2:K2)=0,"",SUM(G2:K2))</f>
         <v/>
       </c>
-      <c r="M2" s="76" t="str">
+      <c r="M2" s="72" t="str">
         <f t="shared" ref="M2:M10" si="1">IF(C2=D2,"",IF(L2="", "", C2-(D2+L2)))</f>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B3" s="64" t="s">
+      <c r="A3" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="70">
         <v>1</v>
       </c>
       <c r="D3" s="27">
         <v>1</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="76">
+      <c r="E3" s="63"/>
+      <c r="F3" s="72">
         <f>IF(D3&gt;0, IF(D3-E3=0,"",D3-E3), IF(E3&gt;0,E3,""))</f>
         <v>1</v>
       </c>
-      <c r="G3" s="64">
+      <c r="G3" s="63">
         <v>1</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="76">
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="72">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M3" s="76" t="str">
+      <c r="M3" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="70">
         <v>4</v>
       </c>
       <c r="D4" s="27">
         <v>1</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="63">
         <v>1</v>
       </c>
-      <c r="F4" s="76" t="str">
+      <c r="F4" s="72" t="str">
         <f t="shared" ref="F4:F10" si="2">IF(D4&gt;0, IF(D4-E4=0,"",D4-E4), IF(E4&gt;0,E4,""))</f>
         <v/>
       </c>
-      <c r="G4" s="64">
+      <c r="G4" s="63">
         <v>1</v>
       </c>
-      <c r="H4" s="64">
+      <c r="H4" s="63">
         <v>1</v>
       </c>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64">
+      <c r="I4" s="63"/>
+      <c r="J4" s="90">
         <v>1</v>
       </c>
-      <c r="K4" s="64"/>
-      <c r="L4" s="76">
+      <c r="K4" s="63"/>
+      <c r="L4" s="72">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="M4" s="76">
+      <c r="M4" s="72">
         <f>IF(C4=D4,"",IF(L4="", "", C4-(D4+L4)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B5" s="64" t="s">
+      <c r="A5" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="74">
+      <c r="C5" s="70">
         <v>1</v>
       </c>
       <c r="D5" s="27">
         <v>1</v>
       </c>
-      <c r="E5" s="64"/>
-      <c r="F5" s="76">
+      <c r="E5" s="63"/>
+      <c r="F5" s="72">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G5" s="64">
+      <c r="G5" s="63">
         <v>1</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="76">
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="72">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M5" s="76" t="str">
+      <c r="M5" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="74">
+      <c r="C6" s="70">
         <v>5</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="63">
         <v>1</v>
       </c>
-      <c r="F6" s="76" t="str">
+      <c r="F6" s="72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G6" s="64">
+      <c r="G6" s="63">
         <v>2</v>
       </c>
-      <c r="H6" s="64">
+      <c r="H6" s="63">
         <v>2</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="76">
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="72">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="M6" s="76">
+      <c r="M6" s="72">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B7" s="64" t="s">
+      <c r="A7" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B7" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="74">
+      <c r="C7" s="70">
         <v>9</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="63">
         <v>2</v>
       </c>
-      <c r="F7" s="76" t="str">
+      <c r="F7" s="72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="63">
         <v>3</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="63">
         <v>2</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="63">
         <v>2</v>
       </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="76">
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="72">
         <f>IF(SUM(G7:K7)=0,"",SUM(G7:K7))</f>
         <v>7</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="72">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B8" s="64" t="s">
+      <c r="A8" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="74">
+      <c r="C8" s="70">
         <v>0</v>
       </c>
       <c r="D8" s="27">
         <v>0</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="76" t="str">
+      <c r="E8" s="63"/>
+      <c r="F8" s="72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="76" t="str">
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="72" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M8" s="76" t="str">
+      <c r="M8" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B9" s="64" t="s">
+      <c r="A9" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="70">
         <v>2</v>
       </c>
       <c r="D9" s="27">
         <v>2</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="63">
         <v>2</v>
       </c>
-      <c r="F9" s="76" t="str">
+      <c r="F9" s="72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="76" t="str">
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="72" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M9" s="76" t="str">
+      <c r="M9" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B10" s="64" t="s">
-        <v>276</v>
+      <c r="A10" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>260</v>
       </c>
       <c r="C10" s="27">
         <v>1</v>
@@ -4275,23 +4035,23 @@
       <c r="D10" s="27">
         <v>1</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="63">
         <v>1</v>
       </c>
-      <c r="F10" s="76" t="str">
+      <c r="F10" s="72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="76" t="str">
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="72" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M10" s="76" t="str">
+      <c r="M10" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4301,751 +4061,753 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="64"/>
-      <c r="B11" s="64" t="s">
-        <v>445</v>
-      </c>
-      <c r="C11" s="75">
+      <c r="A11" s="63"/>
+      <c r="B11" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" s="71">
         <f>SUM(C2:C10)</f>
         <v>24</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="71">
         <f t="shared" ref="D11:M11" si="3">SUM(D2:D10)</f>
         <v>10</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="71">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="71">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="71">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="71">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75">
+      <c r="I11" s="71"/>
+      <c r="J11" s="71">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K11" s="75">
+      <c r="K11" s="71">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="75">
+      <c r="L11" s="71">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="M11" s="75">
+      <c r="M11" s="71">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N11" s="75"/>
+      <c r="N11" s="71"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="64"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B13" s="64" t="s">
+      <c r="A13" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B13" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="70">
         <v>1</v>
       </c>
       <c r="D13" s="27">
         <v>1</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="63">
         <v>1</v>
       </c>
-      <c r="F13" s="76" t="str">
+      <c r="F13" s="72" t="str">
         <f>IF(D13&gt;0, IF(D13-E13=0,"",D13-E13), IF(E13&gt;0,E13,""))</f>
         <v/>
       </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="76" t="str">
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="72" t="str">
         <f t="shared" ref="L13:L17" si="4">IF(SUM(G13:K13)=0,"",SUM(G13:K13))</f>
         <v/>
       </c>
-      <c r="M13" s="76" t="str">
+      <c r="M13" s="72" t="str">
         <f t="shared" ref="M13:M14" si="5">IF(C13=D13,"",IF(L13="", "", C13-(D13+L13)))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B14" s="64" t="s">
+      <c r="A14" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="74">
+      <c r="C14" s="70">
         <v>1</v>
       </c>
       <c r="D14" s="27">
         <v>1</v>
       </c>
-      <c r="E14" s="64"/>
-      <c r="F14" s="76">
+      <c r="E14" s="63"/>
+      <c r="F14" s="72">
         <f>IF(D14&gt;0, IF(D14-E14=0,"",D14-E14), IF(E14&gt;0,E14,""))</f>
         <v>1</v>
       </c>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64">
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63">
         <v>1</v>
       </c>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="76">
+      <c r="J14" s="90">
+        <v>1</v>
+      </c>
+      <c r="K14" s="63"/>
+      <c r="L14" s="72">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M14" s="76" t="str">
+        <v>2</v>
+      </c>
+      <c r="M14" s="72" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B15" s="64" t="s">
+      <c r="A15" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="70">
         <v>4</v>
       </c>
       <c r="D15" s="27">
         <v>1</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="76">
-        <f t="shared" ref="F15:F21" si="6">IF(D15&gt;0, IF(D15-E15=0,"",D15-E15), IF(E15&gt;0,E15,""))</f>
+      <c r="E15" s="63"/>
+      <c r="F15" s="72">
+        <f t="shared" ref="F15:F20" si="6">IF(D15&gt;0, IF(D15-E15=0,"",D15-E15), IF(E15&gt;0,E15,""))</f>
         <v>1</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="63">
         <v>1</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64">
+      <c r="H15" s="63"/>
+      <c r="I15" s="63">
         <v>1</v>
       </c>
-      <c r="J15" s="64">
+      <c r="J15" s="63">
         <v>1</v>
       </c>
-      <c r="K15" s="64"/>
-      <c r="L15" s="76">
+      <c r="K15" s="63"/>
+      <c r="L15" s="72">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="M15" s="76">
+      <c r="M15" s="72">
         <f>IF(C15=D15,"",IF(L15="", "", C15-(D15+L15)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B16" s="64" t="s">
+      <c r="A16" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="74">
+      <c r="C16" s="70">
         <v>3</v>
       </c>
       <c r="D16" s="27">
         <v>1</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="63">
         <v>1</v>
       </c>
-      <c r="F16" s="76" t="str">
+      <c r="F16" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64">
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63">
         <v>1</v>
       </c>
-      <c r="J16" s="64">
+      <c r="J16" s="63">
         <v>1</v>
       </c>
-      <c r="K16" s="64"/>
-      <c r="L16" s="76">
+      <c r="K16" s="63"/>
+      <c r="L16" s="72">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="M16" s="76">
+      <c r="M16" s="72">
         <f t="shared" ref="M16:M21" si="7">IF(C16=D16,"",IF(L16="", "", C16-(D16+L16)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B17" s="64" t="s">
+      <c r="A17" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B17" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="74">
+      <c r="C17" s="70">
         <v>5</v>
       </c>
       <c r="D17" s="27">
         <v>1</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="63">
         <v>1</v>
       </c>
-      <c r="F17" s="76" t="str">
+      <c r="F17" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="63">
         <v>1</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64">
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="90">
         <v>3</v>
       </c>
-      <c r="K17" s="64"/>
-      <c r="L17" s="76">
+      <c r="K17" s="63"/>
+      <c r="L17" s="72">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="M17" s="76">
+      <c r="M17" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B18" s="64" t="s">
+      <c r="A18" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="74">
+      <c r="C18" s="70">
         <v>10</v>
       </c>
       <c r="D18" s="27">
         <v>2</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="63">
         <v>2</v>
       </c>
-      <c r="F18" s="76" t="str">
+      <c r="F18" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="63">
         <v>2</v>
       </c>
-      <c r="H18" s="64">
+      <c r="H18" s="63">
         <v>1</v>
       </c>
-      <c r="I18" s="64">
+      <c r="I18" s="63">
         <v>2</v>
       </c>
-      <c r="J18" s="64">
+      <c r="J18" s="63">
         <v>3</v>
       </c>
-      <c r="K18" s="64"/>
-      <c r="L18" s="76">
+      <c r="K18" s="63"/>
+      <c r="L18" s="72">
         <f>IF(SUM(G18:K18)=0,"",SUM(G18:K18))</f>
         <v>8</v>
       </c>
-      <c r="M18" s="76">
+      <c r="M18" s="72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B19" s="64" t="s">
+      <c r="A19" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="74">
+      <c r="C19" s="70">
         <v>0</v>
       </c>
       <c r="D19" s="27">
         <v>0</v>
       </c>
-      <c r="E19" s="64"/>
-      <c r="F19" s="76" t="str">
+      <c r="E19" s="63"/>
+      <c r="F19" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="76" t="str">
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="72" t="str">
         <f t="shared" ref="L19:L21" si="8">IF(SUM(G19:K19)=0,"",SUM(G19:K19))</f>
         <v/>
       </c>
-      <c r="M19" s="76" t="str">
+      <c r="M19" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B20" s="64" t="s">
+      <c r="A20" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="74">
+      <c r="C20" s="70">
         <v>2</v>
       </c>
       <c r="D20" s="27">
         <v>2</v>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="63">
         <v>2</v>
       </c>
-      <c r="F20" s="76" t="str">
+      <c r="F20" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="76" t="str">
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M20" s="76" t="str">
+      <c r="M20" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B21" s="64" t="s">
-        <v>276</v>
+      <c r="A21" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>260</v>
       </c>
       <c r="C21" s="27">
         <v>0</v>
       </c>
       <c r="D21" s="27"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="76" t="str">
+      <c r="E21" s="63"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="72" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M21" s="76" t="str">
+      <c r="M21" s="72" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N21" s="1">
         <f>SUM(E13:E21)+SUM(L13:L21)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="64" t="s">
-        <v>446</v>
-      </c>
-      <c r="C22" s="75">
+      <c r="B22" s="63" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" s="71">
         <f>SUM(C13:C21)</f>
         <v>26</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="71">
         <f t="shared" ref="D22:M22" si="9">SUM(D13:D21)</f>
         <v>9</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="71">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="71">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="G22" s="75">
+      <c r="G22" s="71">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="H22" s="75">
+      <c r="H22" s="71">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75">
+      <c r="I22" s="71"/>
+      <c r="J22" s="71">
         <f t="shared" si="9"/>
-        <v>8</v>
-      </c>
-      <c r="K22" s="75">
+        <v>9</v>
+      </c>
+      <c r="K22" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L22" s="75">
+      <c r="L22" s="71">
         <f t="shared" si="9"/>
-        <v>18</v>
-      </c>
-      <c r="M22" s="75">
+        <v>19</v>
+      </c>
+      <c r="M22" s="71">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N22" s="75"/>
+      <c r="N22" s="71"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B24" s="64" t="s">
+      <c r="A24" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="74">
+      <c r="C24" s="70">
         <v>1</v>
       </c>
       <c r="D24" s="27">
         <v>1</v>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="63">
         <v>1</v>
       </c>
-      <c r="F24" s="76" t="str">
+      <c r="F24" s="72" t="str">
         <f>IF(D24&gt;0, IF(D24-E24=0,"",D24-E24), IF(E24&gt;0,E24,""))</f>
         <v/>
       </c>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="76" t="str">
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="72" t="str">
         <f t="shared" ref="L24:L28" si="10">IF(SUM(G24:K24)=0,"",SUM(G24:K24))</f>
         <v/>
       </c>
-      <c r="M24" s="76" t="str">
+      <c r="M24" s="72" t="str">
         <f t="shared" ref="M24:M25" si="11">IF(C24=D24,"",IF(L24="", "", C24-(D24+L24)))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B25" s="64" t="s">
+      <c r="A25" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="74">
+      <c r="C25" s="70">
         <v>1</v>
       </c>
       <c r="D25" s="27">
         <v>1</v>
       </c>
-      <c r="E25" s="64"/>
-      <c r="F25" s="76">
+      <c r="E25" s="63"/>
+      <c r="F25" s="72">
         <f>IF(D25&gt;0, IF(D25-E25=0,"",D25-E25), IF(E25&gt;0,E25,""))</f>
         <v>1</v>
       </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64">
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63">
         <v>1</v>
       </c>
-      <c r="K25" s="64"/>
-      <c r="L25" s="76">
+      <c r="K25" s="63"/>
+      <c r="L25" s="72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="M25" s="76" t="str">
+      <c r="M25" s="72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B26" s="64" t="s">
+      <c r="A26" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B26" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="74">
+      <c r="C26" s="70">
         <v>5</v>
       </c>
       <c r="D26" s="27">
         <v>1</v>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="63">
         <v>1</v>
       </c>
-      <c r="F26" s="76" t="str">
+      <c r="F26" s="72" t="str">
         <f t="shared" ref="F26:F32" si="12">IF(D26&gt;0, IF(D26-E26=0,"",D26-E26), IF(E26&gt;0,E26,""))</f>
         <v/>
       </c>
-      <c r="G26" s="64">
+      <c r="G26" s="63">
         <v>1</v>
       </c>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64">
+      <c r="H26" s="63"/>
+      <c r="I26" s="63">
         <v>1</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="63">
         <v>2</v>
       </c>
-      <c r="K26" s="64"/>
-      <c r="L26" s="76">
+      <c r="K26" s="63"/>
+      <c r="L26" s="72">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="M26" s="76">
+      <c r="M26" s="72">
         <f>IF(C26=D26,"",IF(L26="", "", C26-(D26+L26)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B27" s="64" t="s">
+      <c r="A27" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B27" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="74">
+      <c r="C27" s="70">
         <v>2</v>
       </c>
       <c r="D27" s="27">
         <v>1</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="76">
+      <c r="E27" s="63"/>
+      <c r="F27" s="91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64">
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63">
         <v>1</v>
       </c>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="76">
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="72">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="M27" s="76">
+      <c r="M27" s="72">
         <f t="shared" ref="M27:M32" si="13">IF(C27=D27,"",IF(L27="", "", C27-(D27+L27)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B28" s="64" t="s">
+      <c r="A28" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B28" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="74">
+      <c r="C28" s="70">
         <v>5</v>
       </c>
       <c r="D28" s="27">
         <v>1</v>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="63">
         <v>1</v>
       </c>
-      <c r="F28" s="76" t="str">
+      <c r="F28" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64">
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63">
         <v>1</v>
       </c>
-      <c r="J28" s="64">
+      <c r="J28" s="90">
         <v>3</v>
       </c>
-      <c r="K28" s="64"/>
-      <c r="L28" s="76">
+      <c r="K28" s="63"/>
+      <c r="L28" s="72">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="M28" s="76">
+      <c r="M28" s="72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B29" s="64" t="s">
+      <c r="A29" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B29" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="74">
+      <c r="C29" s="70">
         <v>10</v>
       </c>
       <c r="D29" s="27">
         <v>2</v>
       </c>
-      <c r="E29" s="64">
+      <c r="E29" s="63">
         <v>2</v>
       </c>
-      <c r="F29" s="76" t="str">
+      <c r="F29" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G29" s="64">
+      <c r="G29" s="63">
         <v>1</v>
       </c>
-      <c r="H29" s="64">
+      <c r="H29" s="63">
         <v>1</v>
       </c>
-      <c r="I29" s="64">
+      <c r="I29" s="63">
         <v>2</v>
       </c>
-      <c r="J29" s="64">
+      <c r="J29" s="63">
         <v>4</v>
       </c>
-      <c r="K29" s="64"/>
-      <c r="L29" s="76">
+      <c r="K29" s="63"/>
+      <c r="L29" s="72">
         <f>IF(SUM(G29:K29)=0,"",SUM(G29:K29))</f>
         <v>8</v>
       </c>
-      <c r="M29" s="76">
+      <c r="M29" s="72">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B30" s="64" t="s">
+      <c r="A30" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="74">
+      <c r="C30" s="70">
         <v>0</v>
       </c>
       <c r="D30" s="27">
         <v>0</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="76" t="str">
+      <c r="E30" s="63"/>
+      <c r="F30" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="76" t="str">
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="72" t="str">
         <f t="shared" ref="L30:L32" si="14">IF(SUM(G30:K30)=0,"",SUM(G30:K30))</f>
         <v/>
       </c>
-      <c r="M30" s="76" t="str">
+      <c r="M30" s="72" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B31" s="64" t="s">
+      <c r="A31" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B31" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="74">
+      <c r="C31" s="70">
         <v>2</v>
       </c>
       <c r="D31" s="27">
         <v>2</v>
       </c>
-      <c r="E31" s="64">
+      <c r="E31" s="63">
         <v>2</v>
       </c>
-      <c r="F31" s="76" t="str">
+      <c r="F31" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="76" t="str">
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="72" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M31" s="76" t="str">
+      <c r="M31" s="72" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B32" s="64" t="s">
-        <v>276</v>
+      <c r="A32" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>260</v>
       </c>
       <c r="C32" s="27">
         <v>0</v>
       </c>
       <c r="D32" s="27"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="76" t="str">
+      <c r="E32" s="63"/>
+      <c r="F32" s="72" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="76" t="str">
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="72" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M32" s="76" t="str">
+      <c r="M32" s="72" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -5055,51 +4817,51 @@
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C33" s="75">
+      <c r="B33" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="C33" s="71">
         <f>SUM(C24:C32)</f>
         <v>26</v>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="71">
         <f t="shared" ref="D33:M33" si="15">SUM(D24:D32)</f>
         <v>9</v>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="71">
         <f t="shared" si="15"/>
         <v>7</v>
       </c>
-      <c r="F33" s="75">
+      <c r="F33" s="71">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="G33" s="75">
+      <c r="G33" s="71">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="H33" s="75">
+      <c r="H33" s="71">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75">
+      <c r="I33" s="71"/>
+      <c r="J33" s="71">
         <f t="shared" si="15"/>
         <v>10</v>
       </c>
-      <c r="K33" s="75">
+      <c r="K33" s="71">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L33" s="75">
+      <c r="L33" s="71">
         <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="M33" s="75">
+      <c r="M33" s="71">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N33" s="75"/>
+      <c r="N33" s="71"/>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -5147,16 +4909,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>69</v>
@@ -5165,21 +4927,21 @@
         <v>70</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>392</v>
+      <c r="A3" s="63" t="s">
+        <v>358</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>73</v>
@@ -5192,17 +4954,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
-        <v>392</v>
+      <c r="A4" s="63" t="s">
+        <v>358</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>69</v>
@@ -5215,63 +4977,63 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B5" s="64" t="s">
-        <v>405</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>406</v>
+      <c r="A5" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>372</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="E5" s="64" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="64" t="s">
-        <v>412</v>
+      <c r="G5" s="63" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
-        <v>392</v>
-      </c>
-      <c r="B6" s="64" t="s">
-        <v>409</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>407</v>
+      <c r="A6" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>373</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="E6" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="63" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
-        <v>392</v>
+      <c r="A7" s="63" t="s">
+        <v>358</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>69</v>
@@ -5284,17 +5046,17 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
-        <v>392</v>
+      <c r="A8" s="63" t="s">
+        <v>358</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>69</v>
@@ -5307,7 +5069,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="64"/>
+      <c r="A9" s="63"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="10"/>
@@ -5316,121 +5078,121 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="64"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="63"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="62"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="64"/>
+      <c r="A11" s="63"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="19"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="64"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="63"/>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="19"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="64"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>448</v>
-      </c>
-      <c r="C14" s="64" t="s">
+      <c r="A14" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="63" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="9"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
+      <c r="A15" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
+      <c r="A16" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
+      <c r="A17" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
+      <c r="A18" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
+      <c r="A19" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
+      <c r="A20" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
@@ -5451,85 +5213,85 @@
       <c r="G22" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>449</v>
-      </c>
-      <c r="C26" s="64" t="s">
+      <c r="A26" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="C26" s="63" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="9"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
+      <c r="A27" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
+      <c r="A28" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
+      <c r="A29" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
+      <c r="A30" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
+      <c r="A31" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
-        <v>394</v>
-      </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="64"/>
+      <c r="A32" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -5560,526 +5322,526 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>317</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D1" s="68" t="s">
-        <v>339</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="18">
         <v>3587</v>
       </c>
-      <c r="B2" s="67" t="s">
-        <v>312</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>313</v>
+      <c r="B2" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>291</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>3588</v>
       </c>
-      <c r="B3" s="67" t="s">
-        <v>314</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>315</v>
+      <c r="B3" s="66" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>293</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>3596</v>
       </c>
-      <c r="B4" s="67" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>316</v>
+      <c r="B4" s="66" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>294</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>3597</v>
       </c>
-      <c r="B5" s="67" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" s="67" t="s">
-        <v>318</v>
+      <c r="B5" s="66" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>296</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <v>3598</v>
       </c>
-      <c r="B6" s="67" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>320</v>
+      <c r="B6" s="66" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>298</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
         <v>3599</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>321</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>322</v>
+      <c r="B7" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>300</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
         <v>3031</v>
       </c>
-      <c r="B8" s="67" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>324</v>
+      <c r="B8" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="66" t="s">
+        <v>302</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>3032</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>325</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>326</v>
+      <c r="B9" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="66" t="s">
+        <v>304</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>3033</v>
       </c>
-      <c r="B10" s="67" t="s">
-        <v>327</v>
-      </c>
-      <c r="C10" s="67" t="s">
-        <v>328</v>
+      <c r="B10" s="66" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>306</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>3034</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" s="67" t="s">
-        <v>330</v>
+      <c r="B11" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="C11" s="66" t="s">
+        <v>308</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>3548</v>
       </c>
-      <c r="B12" s="67" t="s">
-        <v>331</v>
-      </c>
-      <c r="C12" s="67" t="s">
-        <v>332</v>
+      <c r="B12" s="66" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>310</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>3549</v>
       </c>
-      <c r="B13" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="67" t="s">
-        <v>332</v>
+      <c r="B13" s="66" t="s">
+        <v>311</v>
+      </c>
+      <c r="C13" s="66" t="s">
+        <v>310</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>3136</v>
       </c>
-      <c r="B14" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="C14" s="67" t="s">
-        <v>335</v>
+      <c r="B14" s="66" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>313</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>2105</v>
       </c>
-      <c r="B15" s="67" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="67" t="s">
-        <v>341</v>
+      <c r="B15" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>319</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>2121</v>
       </c>
-      <c r="B16" s="67" t="s">
-        <v>342</v>
-      </c>
-      <c r="C16" s="67" t="s">
-        <v>342</v>
+      <c r="B16" s="66" t="s">
+        <v>320</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>320</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>2133</v>
       </c>
-      <c r="B17" s="67" t="s">
-        <v>343</v>
-      </c>
-      <c r="C17" s="67" t="s">
-        <v>343</v>
+      <c r="B17" s="66" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>321</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>2152</v>
       </c>
-      <c r="B18" s="67" t="s">
-        <v>344</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>344</v>
+      <c r="B18" s="66" t="s">
+        <v>322</v>
+      </c>
+      <c r="C18" s="66" t="s">
+        <v>322</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>2154</v>
       </c>
-      <c r="B19" s="67" t="s">
-        <v>345</v>
-      </c>
-      <c r="C19" s="67" t="s">
-        <v>345</v>
+      <c r="B19" s="66" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>323</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>2314</v>
       </c>
-      <c r="B20" s="67" t="s">
-        <v>346</v>
-      </c>
-      <c r="C20" s="67" t="s">
-        <v>346</v>
+      <c r="B20" s="66" t="s">
+        <v>324</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>324</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>2375</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>347</v>
-      </c>
-      <c r="C21" s="67" t="s">
-        <v>347</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>2410</v>
       </c>
-      <c r="B22" s="67" t="s">
-        <v>348</v>
-      </c>
-      <c r="C22" s="67" t="s">
-        <v>349</v>
+      <c r="B22" s="66" t="s">
+        <v>326</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>327</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>2502</v>
       </c>
-      <c r="B23" s="67" t="s">
-        <v>350</v>
-      </c>
-      <c r="C23" s="67" t="s">
-        <v>351</v>
+      <c r="B23" s="66" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>329</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>7114</v>
       </c>
-      <c r="B24" s="67" t="s">
-        <v>352</v>
-      </c>
-      <c r="C24" s="67" t="s">
-        <v>352</v>
+      <c r="B24" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>330</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="79">
+      <c r="A25" s="75">
         <v>2251</v>
       </c>
-      <c r="B25" s="78" t="s">
-        <v>311</v>
-      </c>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79" t="s">
-        <v>310</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>450</v>
+      <c r="B25" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25" s="74"/>
+      <c r="D25" s="75" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B26" s="67" t="s">
-        <v>366</v>
-      </c>
-      <c r="C26" s="67"/>
+        <v>331</v>
+      </c>
+      <c r="B26" s="66" t="s">
+        <v>344</v>
+      </c>
+      <c r="C26" s="66"/>
       <c r="D26" s="18" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B27" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="67"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="18" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B28" s="67" t="s">
-        <v>354</v>
-      </c>
-      <c r="C28" s="67"/>
+        <v>331</v>
+      </c>
+      <c r="B28" s="66" t="s">
+        <v>332</v>
+      </c>
+      <c r="C28" s="66"/>
       <c r="D28" s="18" t="s">
         <v>57</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B29" s="67" t="s">
-        <v>362</v>
-      </c>
-      <c r="C29" s="67"/>
+        <v>331</v>
+      </c>
+      <c r="B29" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" s="66"/>
       <c r="D29" s="18" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B30" s="67" t="s">
-        <v>363</v>
-      </c>
-      <c r="C30" s="67"/>
+        <v>331</v>
+      </c>
+      <c r="B30" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="66"/>
       <c r="D30" s="18" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B31" s="67" t="s">
-        <v>306</v>
-      </c>
-      <c r="C31" s="67"/>
+        <v>331</v>
+      </c>
+      <c r="B31" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C31" s="66"/>
       <c r="D31" s="18" t="s">
         <v>79</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="67"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
       <c r="D32" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -6130,467 +5892,467 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59" t="s">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59" t="s">
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="66" t="s">
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="66" t="s">
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59" t="s">
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59" t="s">
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59" t="s">
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59" t="s">
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59" t="s">
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59" t="s">
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59" t="s">
+      <c r="C18" s="63"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59" t="s">
+      <c r="C19" s="63"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" s="64"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59" t="s">
+      <c r="B20" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="64" t="s">
-        <v>289</v>
-      </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59" t="s">
+      <c r="B21" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="63"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59" t="s">
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59" t="s">
+      <c r="C24" s="58"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59" t="s">
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="64" t="s">
+      <c r="A26" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59" t="s">
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="64" t="s">
+      <c r="B27" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="57" t="s">
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="64" t="s">
+      <c r="A28" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="64" t="s">
-        <v>302</v>
-      </c>
-      <c r="D28" s="59"/>
-      <c r="E28" s="57" t="s">
+      <c r="B28" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="58"/>
+      <c r="E28" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="64" t="s">
-        <v>305</v>
-      </c>
-      <c r="C29" s="59" t="s">
+      <c r="B29" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="C29" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
+      <c r="A30" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="64" t="s">
+      <c r="B30" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64" t="s">
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6600,7 +6362,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -6608,7 +6370,7 @@
     <col min="10" max="10" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>118</v>
       </c>
@@ -6640,7 +6402,7 @@
         <v>113</v>
       </c>
       <c r="K1" s="29" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="L1" s="29" t="s">
         <v>127</v>
@@ -6648,77 +6410,60 @@
       <c r="M1" s="30" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="89" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
         <v>129</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="H2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="33" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="M2" s="34"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>265</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="15"/>
-      <c r="J3" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="K3" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
       <c r="M3" s="34"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>264</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="16"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
@@ -6726,21 +6471,15 @@
       <c r="H4" s="15"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="L4" s="33"/>
       <c r="M4" s="34"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>264</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="16"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -6748,73 +6487,45 @@
       <c r="H5" s="15"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="L5" s="33"/>
       <c r="M5" s="34"/>
     </row>
-    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>265</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
       <c r="J6" s="15"/>
-      <c r="K6" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="K6" s="33"/>
       <c r="M6" s="34"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>264</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
       <c r="D7" s="16"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="I7" s="33"/>
       <c r="J7" s="15"/>
       <c r="M7" s="34"/>
     </row>
-    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>264</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="16"/>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
@@ -6822,157 +6533,139 @@
       <c r="H8" s="15"/>
       <c r="I8" s="35"/>
       <c r="J8" s="15"/>
-      <c r="L8" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="L8" s="33"/>
       <c r="M8" s="34"/>
     </row>
-    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>264</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>265</v>
-      </c>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
-      <c r="M9" s="33" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="16"/>
+      <c r="M9" s="33"/>
+    </row>
+    <row r="10" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
-      <c r="L10" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="M10" s="34"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="D11" s="16"/>
+      <c r="M10" s="33"/>
+    </row>
+    <row r="11" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
-      <c r="M11" s="33" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="40"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="48" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+      <c r="M11" s="33"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="34"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="M13" s="33"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="39"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
@@ -7038,10 +6731,30 @@
       <c r="A23" s="17"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_tables/input_dataframes.xlsx
+++ b/_tables/input_dataframes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://havforskningsinstituttet.sharepoint.com/sites/DFN_SURVEYS/Shared Documents/DFN_2022_leg 5/Sailing Orders/SailingOrdersDFN/_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{90FBD691-C867-462B-9168-7273C2F6C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F2F5E5F-5B30-416D-9040-698937D22C0B}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{90FBD691-C867-462B-9168-7273C2F6C9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B70E676-66E9-4062-89A0-D0F219C587FA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="757" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="757" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_captions" sheetId="14" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="560">
   <si>
     <t>tab.name</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>envtrans53</t>
+  </si>
+  <si>
+    <t>Leg 5.3 survey map showing transects with acoustics only (yellow lines) and transects with environmental stations in addition (white lines). Super stations and CTD only stations are indicated with red crosses and blue circles, respectively.</t>
   </si>
   <si>
     <t>Survey Name</t>
@@ -705,15 +708,27 @@
     <t>Marek Ostrowski</t>
   </si>
   <si>
+    <t xml:space="preserve">Physical Oceanography Team Leader </t>
+  </si>
+  <si>
     <t>POLAND</t>
   </si>
   <si>
     <t>Mohamed Idrissi</t>
   </si>
   <si>
+    <t>Chemical Oceanography Team Leader (north)</t>
+  </si>
+  <si>
+    <t>idrissi@inrh.ma</t>
+  </si>
+  <si>
     <t>INRH</t>
   </si>
   <si>
+    <t>MOROCCO</t>
+  </si>
+  <si>
     <t>Benjamin Marum</t>
   </si>
   <si>
@@ -723,99 +738,156 @@
     <t>Abdoulie B Jallow </t>
   </si>
   <si>
+    <t>abdouliebjallow@outlook.com</t>
+  </si>
+  <si>
     <t>Belaabed Mohammed</t>
   </si>
   <si>
     <t>belaabed@inrh.ma</t>
   </si>
   <si>
-    <t>MOROCCO</t>
-  </si>
-  <si>
     <t>Mahfoud Bousta</t>
   </si>
   <si>
+    <t>bousta.mahfoud@gmail.com</t>
+  </si>
+  <si>
     <t>Soukaina Ragmane</t>
   </si>
   <si>
+    <t>soukaina.ragmane@gmail.com</t>
+  </si>
+  <si>
     <t>Nasser Kadouri</t>
   </si>
   <si>
+    <t>kaddouri.nassir@gmail.com</t>
+  </si>
+  <si>
     <t>Hassan Obamouh</t>
   </si>
   <si>
+    <t>hassan_oubba@hotmail.fr</t>
+  </si>
+  <si>
+    <t>Nait Hammou Hasnaa</t>
+  </si>
+  <si>
+    <t>NAJD@inrh.ma; hasnaahn1@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed Reda Benallal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plankton </t>
+  </si>
+  <si>
+    <t>benallal-reda@hotmail.fr</t>
+  </si>
+  <si>
+    <t>Hajar Idmoussi</t>
+  </si>
+  <si>
+    <t>hajar.idmoussi@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohmed Ahmed Jeyid  </t>
+  </si>
+  <si>
+    <t>Co-cruise leader (Mauritania). Also fish lab/acoustics</t>
+  </si>
+  <si>
+    <t>moahtaje@yahoo.fr  </t>
+  </si>
+  <si>
+    <t>Sow Harouna</t>
+  </si>
+  <si>
+    <t>swamadou@gmail.com</t>
+  </si>
+  <si>
+    <t>Sleymane Abdel Kerim</t>
+  </si>
+  <si>
+    <t>osouleimane@gmail.com</t>
+  </si>
+  <si>
+    <t>Ba Mamadou Lamba</t>
+  </si>
+  <si>
+    <t>Chemical Oceanography Team Leader (south)</t>
+  </si>
+  <si>
+    <t>ba.mamadoubirane@yahoo.fr</t>
+  </si>
+  <si>
+    <t>Mohamed Salem Abdellahi Chouaib</t>
+  </si>
+  <si>
+    <t>mdsalem69@gmail.com</t>
+  </si>
+  <si>
+    <t>Ibrahima Ndiaya</t>
+  </si>
+  <si>
+    <t>indiaye70@gmail.com</t>
+  </si>
+  <si>
+    <t>Oumar Diéne</t>
+  </si>
+  <si>
+    <t>dieneoumar10@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Ndiaye</t>
+  </si>
+  <si>
+    <t>Jens-Otto Krakstad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diana Zaera-Perez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frøydis Tousgaard Rist </t>
+  </si>
+  <si>
+    <t>Astrid Fuglseth Rasmussen </t>
+  </si>
+  <si>
+    <t>Agnethe Hertzberg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olaf J. Sørås </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jori Neteland-Kyte </t>
+  </si>
+  <si>
+    <t>Mamza Kamal</t>
+  </si>
+  <si>
+    <t>Salahddine Sbiba</t>
+  </si>
+  <si>
+    <t>Ayman Khaili</t>
+  </si>
+  <si>
+    <t>Idrissi Farah Honaida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaymae Achagra </t>
+  </si>
+  <si>
+    <t>Abdelouahab El Haissen</t>
+  </si>
+  <si>
+    <t>Said Charib</t>
+  </si>
+  <si>
     <t>Reda Benallal</t>
   </si>
   <si>
-    <t>Hajar Idmoussi</t>
-  </si>
-  <si>
-    <t>Mohmed Ahmed Jeyid  </t>
-  </si>
-  <si>
-    <t>Sow Harouna</t>
-  </si>
-  <si>
-    <t>Ba Mamadou Lamba</t>
-  </si>
-  <si>
-    <t>Mohamed Salem Abdellahi Chouaib</t>
-  </si>
-  <si>
-    <t>Ismaila Ndour</t>
-  </si>
-  <si>
-    <t>ndismaila@gmail.com</t>
-  </si>
-  <si>
-    <t>dieneoumar10@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Ndiaye</t>
-  </si>
-  <si>
-    <t>Jens-Otto Krakstad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diana Zaera-Perez </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frøydis Tousgaard Rist </t>
-  </si>
-  <si>
-    <t>Astrid Fuglseth Rasmussen </t>
-  </si>
-  <si>
-    <t>Agnethe Hertzberg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olaf J. Sørås </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jori Neteland-Kyte </t>
-  </si>
-  <si>
-    <t>Mamza Kamal</t>
-  </si>
-  <si>
-    <t>Salahddine Sbiba</t>
-  </si>
-  <si>
-    <t>Ayman Khaili</t>
-  </si>
-  <si>
-    <t>Idrissi Farah Honaida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaymae Achagra </t>
-  </si>
-  <si>
-    <t>Abdelouahab El Haissen</t>
-  </si>
-  <si>
-    <t>Said Charib</t>
-  </si>
-  <si>
     <t>Lamin Fofana</t>
   </si>
   <si>
@@ -867,6 +939,21 @@
     <t>ashquambic@gmail.com</t>
   </si>
   <si>
+    <t>The email addresses of a number of the locals seems to have gone wrong!! </t>
+  </si>
+  <si>
+    <t>if they are updated in the input dataframes they will show up here properly, so nice if you can take care of it ;) </t>
+  </si>
+  <si>
+    <t>Also listed on Line 42  </t>
+  </si>
+  <si>
+    <t>Deleted from the input dataframes now </t>
+  </si>
+  <si>
+    <t>Note that if these four Senegalese are all male then we have problems fitting everyone in. I'm confirming this </t>
+  </si>
+  <si>
     <t>SPD Code</t>
   </si>
   <si>
@@ -1336,6 +1423,9 @@
   </si>
   <si>
     <t>Zooplankton biomass estimation</t>
+  </si>
+  <si>
+    <t>Aluminum trays</t>
   </si>
   <si>
     <t>Dried and then frozen</t>
@@ -1609,6 +1699,9 @@
   </si>
   <si>
     <t>Anchovy</t>
+  </si>
+  <si>
+    <t>*Engraulis* sp.</t>
   </si>
   <si>
     <t>PEL1^[list of species is not exhaustive]</t>
@@ -1735,18 +1828,6 @@
     <t>OTHER</t>
   </si>
   <si>
-    <t>*Brachydeuterus auritus*^[may be put under PEL2 but used as Other in 2019]</t>
-  </si>
-  <si>
-    <t>Leg 5.3 survey map showing transects with acoustics only (yellow lines) and transects with environmental stations in addition (white lines). Super stations and CTD only stations are indicated with red crosses and blue circles, respectively.</t>
-  </si>
-  <si>
-    <t>Leg 5.2 survey map showing transects with acoustics only (green lines) and transects with environmental stations in addition (white lines). Super stations and CTD only stations are indicated with red crosses and blue circles, respectively.</t>
-  </si>
-  <si>
-    <t>*Engraulis* sp.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">*Brachydeuterus* </t>
     </r>
@@ -1762,43 +1843,10 @@
     </r>
   </si>
   <si>
-    <t>Fatima zohra Bouthir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plankton </t>
-  </si>
-  <si>
-    <t>Co-cruise leader (Mauritania). Also fish lab/acoustics</t>
-  </si>
-  <si>
-    <t>moahtaje@yahoo.fr  </t>
-  </si>
-  <si>
-    <t>Sleymane Abdel Kerim</t>
-  </si>
-  <si>
-    <t>Mohmed Ahmed Jeyi  d</t>
-  </si>
-  <si>
-    <t>Oumar Diéne</t>
-  </si>
-  <si>
-    <t>The email addresses of a number of the locals seems to have gone wrong!! </t>
-  </si>
-  <si>
-    <t>if they are updated in the input dataframes they will show up here properly, so nice if you can take care of it ;) </t>
-  </si>
-  <si>
-    <t>Also listed on Line 42  </t>
-  </si>
-  <si>
-    <t>Deleted from the input dataframes now </t>
-  </si>
-  <si>
-    <t>Note that if these four Senegalese are all male then we have problems fitting everyone in. I'm confirming this </t>
-  </si>
-  <si>
-    <t>Aluminum trays</t>
+    <t>*Brachydeuterus auritus*^[may be put under PEL2 but used as Other in 2019]</t>
+  </si>
+  <si>
+    <t>Leg 5.2 survey map showing transects with acoustics only (green lines) and transects with environmental stations in addition (white lines). Super stations and CTD only stations are indicated with red crosses and blue circles, respectively. The leg includes a master transect off Dhakla.</t>
   </si>
 </sst>
 </file>
@@ -2057,7 +2105,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2121,6 +2169,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -2385,7 +2439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2630,6 +2684,11 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2656,9 +2715,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3093,51 +3149,51 @@
   <sheetData>
     <row r="1" spans="1:32" s="31" customFormat="1" ht="69" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="J1" s="33" t="s">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>406</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="78" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="E2" s="79"/>
       <c r="F2" s="79"/>
@@ -3169,16 +3225,16 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="78" t="s">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="D3" s="79" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="E3" s="79"/>
       <c r="F3" s="79"/>
@@ -3243,29 +3299,29 @@
     </row>
     <row r="5" spans="1:32" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="78" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="B5" s="89" t="s">
-        <v>413</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>543</v>
+        <v>442</v>
+      </c>
+      <c r="C5" s="104" t="s">
+        <v>443</v>
       </c>
       <c r="D5" s="78" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="101" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="101" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H5" s="101" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="I5" s="101" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="J5" s="91"/>
       <c r="K5" s="91"/>
@@ -3292,29 +3348,29 @@
     </row>
     <row r="6" spans="1:32" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="78" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="D6" s="78" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="E6" s="89"/>
       <c r="F6" s="101" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="101" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H6" s="101" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I6" s="102" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="J6" s="91"/>
       <c r="K6" s="91"/>
@@ -3341,7 +3397,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="94" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="B7" s="84"/>
       <c r="C7" s="84"/>
@@ -3376,29 +3432,29 @@
     </row>
     <row r="8" spans="1:32" s="77" customFormat="1" ht="23" x14ac:dyDescent="0.35">
       <c r="A8" s="89" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="B8" s="89" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="D8" s="78" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="E8" s="78"/>
       <c r="F8" s="90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="90" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H8" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I8" s="93" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="K8" s="95"/>
       <c r="L8"/>
@@ -3425,29 +3481,29 @@
     </row>
     <row r="9" spans="1:32" s="77" customFormat="1" ht="23" x14ac:dyDescent="0.35">
       <c r="A9" s="89" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C9" s="78" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="D9" s="78" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="E9" s="78"/>
       <c r="F9" s="90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" s="90" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H9" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I9" s="93" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="J9" s="95"/>
       <c r="K9" s="95"/>
@@ -3475,29 +3531,29 @@
     </row>
     <row r="10" spans="1:32" s="77" customFormat="1" ht="34.5" x14ac:dyDescent="0.35">
       <c r="A10" s="89" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="B10" s="89" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="D10" s="78" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="E10" s="78"/>
       <c r="F10" s="90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" s="90" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H10" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I10" s="93" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="J10" s="95"/>
       <c r="K10" s="95"/>
@@ -3557,30 +3613,30 @@
       <c r="AF11" s="83"/>
     </row>
     <row r="12" spans="1:32" ht="23" x14ac:dyDescent="0.35">
-      <c r="A12" s="104" t="s">
-        <v>432</v>
+      <c r="A12" s="107" t="s">
+        <v>462</v>
       </c>
       <c r="B12" s="99" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="C12" s="79" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="D12" s="79" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="E12" s="79"/>
       <c r="F12" s="90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="90" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H12" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I12" s="93" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="J12" s="82"/>
       <c r="K12" s="82"/>
@@ -3606,28 +3662,28 @@
       <c r="AF12" s="83"/>
     </row>
     <row r="13" spans="1:32" ht="46" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="107"/>
       <c r="B13" s="89" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="D13" s="78" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="E13" s="78"/>
       <c r="F13" s="90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13" s="90" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H13" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I13" s="93" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="J13" s="90"/>
       <c r="K13" s="90"/>
@@ -3653,28 +3709,28 @@
       <c r="AF13" s="83"/>
     </row>
     <row r="14" spans="1:32" ht="46" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="89" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="D14" s="78" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="E14" s="78"/>
       <c r="F14" s="103" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" s="103" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="H14" s="103" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I14" s="103" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="J14" s="90"/>
       <c r="K14" s="90"/>
@@ -3734,25 +3790,25 @@
     </row>
     <row r="16" spans="1:32" ht="23" x14ac:dyDescent="0.35">
       <c r="A16" s="89" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="D16" s="78" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="E16" s="78"/>
       <c r="F16" s="78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="78"/>
       <c r="H16" s="100"/>
       <c r="I16" s="89" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="J16" s="90"/>
       <c r="K16" s="90"/>
@@ -3779,29 +3835,29 @@
     </row>
     <row r="17" spans="1:32" ht="34.5" x14ac:dyDescent="0.35">
       <c r="A17" s="89" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="C17" s="78" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="E17" s="78"/>
       <c r="F17" s="78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" s="78" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="H17" s="90" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="I17" s="90" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="J17" s="90"/>
       <c r="K17" s="90"/>
@@ -3846,68 +3902,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="65" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A2" s="67" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="B2" s="68" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A3" s="67" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A5" s="67" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A6" s="67" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -3928,124 +3984,124 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="35" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="110" t="s">
-        <v>470</v>
-      </c>
-      <c r="B2" s="111" t="s">
-        <v>471</v>
-      </c>
-      <c r="C2" s="109" t="s">
-        <v>472</v>
+      <c r="A2" s="113" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" s="114" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" s="112" t="s">
+        <v>502</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="111"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="109"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="112"/>
       <c r="D3" s="47" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="107" t="s">
-        <v>475</v>
-      </c>
-      <c r="B4" s="107" t="s">
-        <v>476</v>
-      </c>
-      <c r="C4" s="112" t="s">
-        <v>477</v>
+      <c r="A4" s="110" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4" s="110" t="s">
+        <v>506</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>507</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="107"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="112"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="115"/>
       <c r="D5" s="47" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="107"/>
-      <c r="B6" s="107"/>
-      <c r="C6" s="112"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="115"/>
       <c r="D6" s="47" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="37" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="43" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A10" s="37" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4053,21 +4109,21 @@
       <c r="B11" s="36"/>
       <c r="C11" s="52"/>
       <c r="D11" s="52" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="37" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4075,7 +4131,7 @@
       <c r="B13" s="36"/>
       <c r="C13" s="53"/>
       <c r="D13" s="47" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -4083,7 +4139,7 @@
       <c r="B14" s="36"/>
       <c r="C14" s="53"/>
       <c r="D14" s="47" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4091,17 +4147,17 @@
       <c r="B15" s="36"/>
       <c r="C15" s="53"/>
       <c r="D15" s="47" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="39"/>
       <c r="B16" s="36"/>
       <c r="C16" s="36" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4109,27 +4165,27 @@
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="47" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="39"/>
       <c r="B18" s="36"/>
       <c r="C18" s="36" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="39"/>
       <c r="B19" s="36"/>
       <c r="C19" s="36" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4137,21 +4193,21 @@
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
       <c r="D20" s="47" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="37" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4159,7 +4215,7 @@
       <c r="B22" s="36"/>
       <c r="C22" s="53"/>
       <c r="D22" s="47" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4167,17 +4223,17 @@
       <c r="B23" s="36"/>
       <c r="C23" s="53"/>
       <c r="D23" s="47" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="36"/>
       <c r="B24" s="36"/>
       <c r="C24" s="36" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4185,7 +4241,7 @@
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
       <c r="D25" s="47" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4193,67 +4249,67 @@
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="42" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="107" t="s">
-        <v>517</v>
-      </c>
-      <c r="B27" s="107" t="s">
-        <v>518</v>
-      </c>
-      <c r="C27" s="105" t="s">
-        <v>519</v>
+      <c r="A27" s="110" t="s">
+        <v>548</v>
+      </c>
+      <c r="B27" s="110" t="s">
+        <v>549</v>
+      </c>
+      <c r="C27" s="108" t="s">
+        <v>550</v>
       </c>
       <c r="D27" s="76" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
-      <c r="C28" s="106"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="109"/>
       <c r="D28" s="76" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="37" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="D29" s="37"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="37" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D30" s="37"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -4359,7 +4415,7 @@
         <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -4367,7 +4423,7 @@
         <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>527</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4391,82 +4447,82 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="4">
         <v>13</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4">
         <v>25</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>29</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4488,79 +4544,79 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -4621,54 +4677,54 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="48">
         <v>1</v>
@@ -4699,10 +4755,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" s="48">
         <v>1</v>
@@ -4717,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -4733,10 +4789,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C4" s="48">
         <v>4</v>
@@ -4773,10 +4829,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="48">
         <v>2</v>
@@ -4807,10 +4863,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="48">
         <v>5</v>
@@ -4845,10 +4901,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="48">
         <v>9</v>
@@ -4885,10 +4941,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="48">
         <v>0</v>
@@ -4917,10 +4973,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="48">
         <v>3</v>
@@ -4951,10 +5007,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="20">
         <v>1</v>
@@ -4990,7 +5046,7 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="49">
         <f>SUM(C2:C10)</f>
@@ -5056,10 +5112,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="48">
         <v>1</v>
@@ -5090,10 +5146,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="48">
         <v>1</v>
@@ -5110,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="59" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="50">
@@ -5124,10 +5180,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="48">
         <v>4</v>
@@ -5162,10 +5218,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="48">
         <v>3</v>
@@ -5200,10 +5256,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="48">
         <v>5</v>
@@ -5238,10 +5294,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" s="48">
         <v>10</v>
@@ -5280,10 +5336,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="48">
         <v>0</v>
@@ -5312,10 +5368,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="48">
         <v>2</v>
@@ -5346,10 +5402,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="20">
         <v>0</v>
@@ -5377,7 +5433,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="49">
         <f>SUM(C13:C21)</f>
@@ -5427,10 +5483,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="48">
         <v>1</v>
@@ -5461,10 +5517,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="48">
         <v>1</v>
@@ -5493,10 +5549,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="48">
         <v>5</v>
@@ -5533,10 +5589,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="48">
         <v>2</v>
@@ -5567,10 +5623,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" s="48">
         <v>5</v>
@@ -5605,10 +5661,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" s="48">
         <v>10</v>
@@ -5647,10 +5703,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" s="48">
         <v>0</v>
@@ -5679,10 +5735,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" s="48">
         <v>2</v>
@@ -5713,10 +5769,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" s="20">
         <v>0</v>
@@ -5747,7 +5803,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C33" s="49">
         <f>SUM(C24:C32)</f>
@@ -5819,1415 +5875,1450 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" t="s">
         <v>174</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" t="s">
-        <v>172</v>
-      </c>
-      <c r="G17" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="G19" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F26" s="70" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" s="8"/>
+        <v>207</v>
+      </c>
+      <c r="D31" s="105" t="s">
+        <v>208</v>
+      </c>
       <c r="E31" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" s="60"/>
+        <v>169</v>
+      </c>
+      <c r="D34" s="105" t="s">
+        <v>214</v>
+      </c>
       <c r="E34" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="G35" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="E35" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="D36" s="105" t="s">
+        <v>218</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="D37" s="106" t="s">
+        <v>220</v>
       </c>
       <c r="E37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F37" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C38" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="D38" s="105" t="s">
+        <v>222</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="D39" s="106" t="s">
+        <v>224</v>
       </c>
       <c r="E39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
-        <v>531</v>
+        <v>225</v>
       </c>
       <c r="C40" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="D40" s="105" t="s">
+        <v>226</v>
       </c>
       <c r="E40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C41" t="s">
-        <v>532</v>
+        <v>228</v>
+      </c>
+      <c r="D41" s="105" t="s">
+        <v>229</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F41" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
-        <v>532</v>
+        <v>228</v>
+      </c>
+      <c r="D42" s="105" t="s">
+        <v>231</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F42" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C43" t="s">
-        <v>533</v>
+        <v>233</v>
       </c>
       <c r="D43" t="s">
-        <v>534</v>
+        <v>234</v>
       </c>
       <c r="E43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="D44" s="105" t="s">
+        <v>236</v>
       </c>
       <c r="E44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>535</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="D45" s="105" t="s">
+        <v>238</v>
       </c>
       <c r="E45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
-        <v>536</v>
-      </c>
-      <c r="C46" t="s">
-        <v>102</v>
+        <v>239</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="105" t="s">
+        <v>241</v>
       </c>
       <c r="E46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C47" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="D47" s="105" t="s">
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>180</v>
+        <v>161</v>
+      </c>
+      <c r="D48" s="105" t="s">
+        <v>178</v>
       </c>
       <c r="E48" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="G48" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="C49" t="s">
-        <v>160</v>
-      </c>
-      <c r="D49" t="s">
-        <v>177</v>
+        <v>164</v>
+      </c>
+      <c r="D49" s="105" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" t="s">
+        <v>127</v>
       </c>
       <c r="G49" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C50" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" t="s">
-        <v>223</v>
+        <v>169</v>
+      </c>
+      <c r="D50" s="105" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" t="s">
+        <v>127</v>
       </c>
       <c r="G50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>537</v>
+        <v>248</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
-      </c>
-      <c r="D51" t="s">
-        <v>224</v>
+        <v>169</v>
+      </c>
+      <c r="D51" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="E51" t="s">
+        <v>127</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>225</v>
-      </c>
-      <c r="C52" t="s">
-        <v>168</v>
-      </c>
-      <c r="D52" t="s">
-        <v>189</v>
-      </c>
-      <c r="G52" t="s">
-        <v>158</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C52"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D53" s="62"/>
       <c r="E53" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D54" s="63"/>
       <c r="E54" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D55" s="63"/>
       <c r="E55" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D56" s="63"/>
       <c r="E56" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D57" s="63"/>
       <c r="E57" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D58" s="63"/>
       <c r="E58" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D59" s="63"/>
       <c r="E59" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D60" s="60"/>
       <c r="E60" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F60" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D61" s="61"/>
       <c r="E61" s="61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F61" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D62" s="60"/>
       <c r="E62" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F62" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D63" s="61"/>
       <c r="E63" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F63" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D64" s="60"/>
       <c r="E64" s="60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D65" s="60"/>
       <c r="E65" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D66" s="60"/>
       <c r="E66" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -7237,172 +7328,172 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D68" s="61"/>
       <c r="E68" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F68" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E69" s="60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G69" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D72" s="69" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="E72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D73" s="69" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D74" s="69" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="E74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D75" s="69" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="69" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.35">
@@ -7492,27 +7583,27 @@
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>538</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>539</v>
+        <v>282</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>540</v>
+        <v>283</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>541</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>542</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -7566,19 +7657,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="D1" s="46" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -7586,16 +7677,16 @@
         <v>3587</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -7603,16 +7694,16 @@
         <v>3588</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -7620,16 +7711,16 @@
         <v>3596</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -7637,16 +7728,16 @@
         <v>3597</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -7654,16 +7745,16 @@
         <v>3598</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>272</v>
+        <v>301</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -7671,16 +7762,16 @@
         <v>3599</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -7688,16 +7779,16 @@
         <v>3031</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -7705,16 +7796,16 @@
         <v>3032</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -7722,16 +7813,16 @@
         <v>3033</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -7739,16 +7830,16 @@
         <v>3034</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -7756,16 +7847,16 @@
         <v>3548</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -7773,16 +7864,16 @@
         <v>3549</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -7790,16 +7881,16 @@
         <v>3136</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -7807,16 +7898,16 @@
         <v>2105</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -7824,16 +7915,16 @@
         <v>2121</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -7841,16 +7932,16 @@
         <v>2133</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -7858,16 +7949,16 @@
         <v>2152</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -7875,16 +7966,16 @@
         <v>2154</v>
       </c>
       <c r="B19" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>294</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>294</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -7892,16 +7983,16 @@
         <v>2314</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -7909,16 +8000,16 @@
         <v>2375</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -7926,16 +8017,16 @@
         <v>2410</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -7943,16 +8034,16 @@
         <v>2502</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -7960,16 +8051,16 @@
         <v>7114</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -7977,104 +8068,104 @@
         <v>2251</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="14" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="14" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="14" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="14" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="C31" s="45"/>
       <c r="D31" s="14" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -8082,10 +8173,10 @@
       <c r="B32" s="45"/>
       <c r="C32" s="45"/>
       <c r="D32" s="14" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -8111,39 +8202,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D2" s="41"/>
       <c r="E2" s="41"/>
@@ -8153,61 +8244,61 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
       <c r="F3" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G3" s="41"/>
       <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
       <c r="F4" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="C5" s="41"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
       <c r="F5" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G5" s="41"/>
       <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D6" s="41"/>
       <c r="E6" s="41"/>
@@ -8217,77 +8308,77 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="C7" s="41"/>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
       <c r="F7" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G7" s="41"/>
       <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="C8" s="41"/>
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
       <c r="F8" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G8" s="41"/>
       <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="41"/>
       <c r="E9" s="41"/>
       <c r="F9" s="44" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G9" s="41"/>
       <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="41"/>
       <c r="E10" s="3"/>
       <c r="F10" s="44" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G10" s="41"/>
       <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D11" s="41"/>
       <c r="E11" s="41"/>
@@ -8297,15 +8388,15 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="C12" s="41"/>
       <c r="D12" s="41"/>
       <c r="E12" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="41"/>
@@ -8313,15 +8404,15 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="41"/>
       <c r="E13" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F13" s="41"/>
       <c r="G13" s="41"/>
@@ -8329,15 +8420,15 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
       <c r="E14" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F14" s="41"/>
       <c r="G14" s="41"/>
@@ -8345,31 +8436,31 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="C15" s="41"/>
       <c r="D15" s="41"/>
       <c r="E15" s="41"/>
       <c r="F15" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>313</v>
       </c>
       <c r="C16" s="41"/>
       <c r="D16" s="41"/>
       <c r="E16" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F16" s="41"/>
       <c r="G16" s="41"/>
@@ -8377,14 +8468,14 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
@@ -8393,14 +8484,14 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="41"/>
@@ -8409,14 +8500,14 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="41"/>
@@ -8425,14 +8516,14 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E20" s="41"/>
       <c r="F20" s="41"/>
@@ -8441,13 +8532,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -8457,13 +8548,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
@@ -8473,14 +8564,14 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="C23" s="41"/>
       <c r="D23" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41"/>
@@ -8489,30 +8580,30 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="C24" s="41"/>
       <c r="D24" s="3"/>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="C25" s="41"/>
       <c r="D25" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
@@ -8521,60 +8612,60 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
       <c r="F26" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G26" s="41"/>
       <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
       <c r="F27" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G27" s="41"/>
       <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="D28" s="41"/>
       <c r="E28" s="41"/>
       <c r="F28" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="G28" s="41"/>
       <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D29" s="41"/>
       <c r="E29" s="41"/>
@@ -8584,14 +8675,14 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="41" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="3"/>
@@ -8619,40 +8710,40 @@
   <sheetData>
     <row r="1" spans="1:19" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="P1" s="74"/>
       <c r="Q1" s="11"/>
@@ -8661,16 +8752,16 @@
     </row>
     <row r="2" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
@@ -8685,16 +8776,16 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="24" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="12"/>
@@ -8709,16 +8800,16 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -8733,20 +8824,20 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="26" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="G5" s="11"/>
       <c r="I5" s="11"/>
@@ -8759,16 +8850,16 @@
     </row>
     <row r="6" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -8783,16 +8874,16 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -8807,16 +8898,16 @@
     </row>
     <row r="8" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -8831,16 +8922,16 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -8855,16 +8946,16 @@
     </row>
     <row r="10" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="24" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="12"/>
@@ -8879,16 +8970,16 @@
     </row>
     <row r="11" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="12"/>
@@ -8903,16 +8994,16 @@
     </row>
     <row r="12" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="12"/>
@@ -8927,16 +9018,16 @@
     </row>
     <row r="13" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="12"/>
@@ -8951,16 +9042,16 @@
     </row>
     <row r="14" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="24" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="12"/>
@@ -8988,10 +9079,10 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="29"/>
@@ -9006,10 +9097,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -9023,10 +9114,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="26" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -9410,15 +9501,15 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349F0C36-44B1-4390-B047-386ADF46CBDE}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="c01e712b-8f9b-4625-8219-31b20605feb3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="2b166a80-dccc-42cc-be33-87bca7e0d87c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
